--- a/data/Cuadros_oficiales_por_carrera.xlsx
+++ b/data/Cuadros_oficiales_por_carrera.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,12 @@
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002A78D6"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -100,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,6 +145,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -507,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1121,578 +1133,906 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Competencias</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>ADMP0124</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>CE4 / CT4</t>
+        </is>
+      </c>
+      <c r="I31" s="18" t="n">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>ADMP0119</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>CE4 / CT4</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="16" t="n"/>
+      <c r="H32" s="16" t="n"/>
+      <c r="I32" s="19" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>ADMP0112</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>CE2 / CT2</t>
+        </is>
+      </c>
+      <c r="I33" s="18" t="n">
+        <v>91.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>══ TA2 — 63 estudiantes ══</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Promedio %</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Nivel</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Mediana %</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>Mínimo %</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>Máximo %</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>Desv.</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>% Insuf.</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>% En des.</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>% Satisf./Sobres.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="n">
+    <row r="39">
+      <c r="A39" s="8" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="C32" s="8" t="n">
+      <c r="C39" s="8" t="n">
         <v>83.3</v>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="D39" s="8" t="n">
         <v>37.5</v>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="E39" s="8" t="n">
         <v>95.8</v>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="F39" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="G32" s="8" t="n">
+      <c r="G39" s="8" t="n">
         <v>3.2</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H39" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>55.6 / 27.0</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Distribución (N° estud.):</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>Insuf: 2</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>En des: 9</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>Satisf: 35</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>Sobres: 17</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>Total: 63</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="n"/>
-      <c r="I35" s="6" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="n"/>
+      <c r="I42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>N° preg.</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>Prom. logro %</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>Nivel</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>% Insuf.</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>% En des.</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>% Satisf.</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>% Sobres.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>CE1</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C37" s="8" t="n">
+      <c r="C44" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D37" s="8" t="n">
+      <c r="D44" s="8" t="n">
         <v>59.3</v>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>En desarrollo (ED)</t>
         </is>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="F44" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="G37" s="8" t="n">
+      <c r="G44" s="8" t="n">
         <v>61.9</v>
       </c>
-      <c r="H37" s="8" t="n">
+      <c r="H44" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="I37" s="8" t="n">
+      <c r="I44" s="8" t="n">
         <v>3.2</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>CE2</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="C45" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="D45" s="12" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>3.2</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>14.3</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="I45" s="12" t="n">
         <v>60.3</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>CE3</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C39" s="8" t="n">
+      <c r="C46" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="D46" s="8" t="n">
         <v>86.2</v>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F46" s="8" t="n">
         <v>1.6</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G46" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H46" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="I39" s="8" t="n">
+      <c r="I46" s="8" t="n">
         <v>47.6</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>CE4</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n">
+      <c r="C47" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D40" s="12" t="n">
+      <c r="D47" s="12" t="n">
         <v>85.7</v>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>1.6</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H40" s="12" t="n">
+      <c r="H47" s="12" t="n">
         <v>33.3</v>
       </c>
-      <c r="I40" s="12" t="n">
+      <c r="I47" s="12" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>CT1</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C41" s="8" t="n">
+      <c r="C48" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="D48" s="8" t="n">
         <v>59.3</v>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t>En desarrollo (ED)</t>
         </is>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F48" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="G41" s="8" t="n">
+      <c r="G48" s="8" t="n">
         <v>61.9</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H48" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="I41" s="8" t="n">
+      <c r="I48" s="8" t="n">
         <v>3.2</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>CT2</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C42" s="12" t="n">
+      <c r="C49" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D42" s="12" t="n">
+      <c r="D49" s="12" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>3.2</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>14.3</v>
       </c>
-      <c r="H42" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="I42" s="12" t="n">
+      <c r="I49" s="12" t="n">
         <v>60.3</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>CT3</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C43" s="8" t="n">
+      <c r="C50" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D43" s="8" t="n">
+      <c r="D50" s="8" t="n">
         <v>86.2</v>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F43" s="8" t="n">
+      <c r="F50" s="8" t="n">
         <v>1.6</v>
       </c>
-      <c r="G43" s="8" t="n">
+      <c r="G50" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H50" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="I43" s="8" t="n">
+      <c r="I50" s="8" t="n">
         <v>47.6</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>CT4</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n">
+      <c r="C51" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D44" s="12" t="n">
+      <c r="D51" s="12" t="n">
         <v>85.7</v>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>1.6</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H44" s="12" t="n">
+      <c r="H51" s="12" t="n">
         <v>33.3</v>
       </c>
-      <c r="I44" s="12" t="n">
+      <c r="I51" s="12" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="6" t="n"/>
-      <c r="I46" s="6" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="6" t="n"/>
+      <c r="I53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>Competencias</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>% Aciertos</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>ADMP0201</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>CE1 / CT1</t>
         </is>
       </c>
-      <c r="I48" s="14" t="n">
+      <c r="I55" s="14" t="n">
         <v>25.4</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>ADMP0202</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>CE1 / CT1</t>
         </is>
       </c>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
-      <c r="G49" s="16" t="n"/>
-      <c r="H49" s="16" t="n"/>
-      <c r="I49" s="17" t="n">
+      <c r="C56" s="16" t="n"/>
+      <c r="D56" s="16" t="n"/>
+      <c r="E56" s="16" t="n"/>
+      <c r="F56" s="16" t="n"/>
+      <c r="G56" s="16" t="n"/>
+      <c r="H56" s="16" t="n"/>
+      <c r="I56" s="17" t="n">
         <v>31.7</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="6" t="n"/>
+      <c r="G59" s="6" t="n"/>
+      <c r="H59" s="6" t="n"/>
+      <c r="I59" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Competencias</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>ADMP0212</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>CE2 / CT2</t>
+        </is>
+      </c>
+      <c r="I61" s="18" t="n">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>ADMP0211</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>CE2 / CT2</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="n"/>
+      <c r="D62" s="16" t="n"/>
+      <c r="E62" s="16" t="n"/>
+      <c r="F62" s="16" t="n"/>
+      <c r="G62" s="16" t="n"/>
+      <c r="H62" s="16" t="n"/>
+      <c r="I62" s="19" t="n">
+        <v>95.2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>ADMP0217</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT3</t>
+        </is>
+      </c>
+      <c r="I63" s="18" t="n">
+        <v>95.2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>ADMP0210</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>CE2 / CT2</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="n"/>
+      <c r="D64" s="16" t="n"/>
+      <c r="E64" s="16" t="n"/>
+      <c r="F64" s="16" t="n"/>
+      <c r="G64" s="16" t="n"/>
+      <c r="H64" s="16" t="n"/>
+      <c r="I64" s="19" t="n">
+        <v>93.7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>ADMP0206</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CT1</t>
+        </is>
+      </c>
+      <c r="I65" s="18" t="n">
+        <v>93.7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>ADMP0221</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>CE4 / CT4</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="n"/>
+      <c r="D66" s="16" t="n"/>
+      <c r="E66" s="16" t="n"/>
+      <c r="F66" s="16" t="n"/>
+      <c r="G66" s="16" t="n"/>
+      <c r="H66" s="16" t="n"/>
+      <c r="I66" s="19" t="n">
+        <v>92.09999999999999</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>ADMP0214</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT3</t>
+        </is>
+      </c>
+      <c r="I67" s="18" t="n">
+        <v>92.09999999999999</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>ADMP0222</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>CE4 / CT4</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="n"/>
+      <c r="D68" s="16" t="n"/>
+      <c r="E68" s="16" t="n"/>
+      <c r="F68" s="16" t="n"/>
+      <c r="G68" s="16" t="n"/>
+      <c r="H68" s="16" t="n"/>
+      <c r="I68" s="19" t="n">
+        <v>90.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>ADMP0216</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT3</t>
+        </is>
+      </c>
+      <c r="I69" s="18" t="n">
+        <v>90.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>ADMP0203</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>CE1 / CT1</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="n"/>
+      <c r="D70" s="16" t="n"/>
+      <c r="E70" s="16" t="n"/>
+      <c r="F70" s="16" t="n"/>
+      <c r="G70" s="16" t="n"/>
+      <c r="H70" s="16" t="n"/>
+      <c r="I70" s="19" t="n">
+        <v>90.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>ADMP0223</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>CE4 / CT4</t>
+        </is>
+      </c>
+      <c r="I71" s="18" t="n">
+        <v>90.5</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="B49:H49"/>
+  <mergeCells count="38">
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B68:H68"/>
+    <mergeCell ref="B55:H55"/>
     <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B64:H64"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="H40:I40"/>
     <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="B32:H32"/>
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A42:I42"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="B62:H62"/>
     <mergeCell ref="B25:H25"/>
-    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A53:I53"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B31:H31"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B66:H66"/>
+    <mergeCell ref="B56:H56"/>
     <mergeCell ref="A10:I10"/>
-    <mergeCell ref="B48:H48"/>
-    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="B71:H71"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="B70:H70"/>
+    <mergeCell ref="B60:H60"/>
+    <mergeCell ref="B67:H67"/>
     <mergeCell ref="B23:H23"/>
-    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="B69:H69"/>
     <mergeCell ref="H8:I8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1705,7 +2045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2284,151 +2624,71 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Competencias</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>CAUP0111</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>CE2 / CT2</t>
+        </is>
+      </c>
+      <c r="I30" s="18" t="n">
+        <v>94.8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>══ TA2 — 86 estudiantes ══</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Resultado global de cohorte</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Promedio %</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Nivel</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Mediana %</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Mínimo %</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>Máximo %</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>Desv.</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>% Insuf.</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>% En des.</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>% Satisf./Sobres.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Satisfactorio (S)</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>48.8 / 11.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>Distribución (N° estud.):</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Insuf: 2</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>En des: 32</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>Satisf: 42</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>Sobres: 10</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t>Total: 86</t>
-        </is>
-      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Logro y distribución por competencia</t>
+          <t>Resultado global de cohorte</t>
         </is>
       </c>
       <c r="B34" s="6" t="n"/>
@@ -2443,457 +2703,751 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
+          <t>Promedio %</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Nivel</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Mediana %</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Mínimo %</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Máximo %</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Desv.</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>% Insuf.</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>% En des.</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>% Satisf./Sobres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Satisfactorio (S)</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>48.8 / 11.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Distribución (N° estud.):</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Insuf: 2</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>En des: 32</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Satisf: 42</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>Sobres: 10</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Total: 86</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Logro y distribución por competencia</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>N° preg.</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>Prom. logro %</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>Nivel</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>% Insuf.</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>% En des.</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>% Satisf.</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>% Sobres.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>CE1</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C36" s="8" t="n">
+      <c r="C41" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D41" s="8" t="n">
         <v>63</v>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>En desarrollo (ED)</t>
         </is>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F41" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G41" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="H41" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="I36" s="8" t="n">
+      <c r="I41" s="8" t="n">
         <v>11.6</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>CE2</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n">
+      <c r="C42" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D37" s="12" t="n">
+      <c r="D42" s="12" t="n">
         <v>79.5</v>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>2.3</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>32.6</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="H42" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="I42" s="12" t="n">
         <v>22.1</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>CE3</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C38" s="8" t="n">
+      <c r="C43" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D43" s="8" t="n">
         <v>72.7</v>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F43" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="G38" s="8" t="n">
+      <c r="G43" s="8" t="n">
         <v>46.5</v>
       </c>
-      <c r="H38" s="8" t="n">
+      <c r="H43" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="I38" s="8" t="n">
+      <c r="I43" s="8" t="n">
         <v>17.4</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>CE4</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n">
+      <c r="C44" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D44" s="12" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>1.2</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>37.2</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="I44" s="12" t="n">
         <v>18.6</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>CT1</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C40" s="8" t="n">
+      <c r="C45" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="D45" s="8" t="n">
         <v>67.09999999999999</v>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>En desarrollo (ED)</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F45" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="G40" s="8" t="n">
+      <c r="G45" s="8" t="n">
         <v>55.8</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="H45" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="I40" s="8" t="n">
+      <c r="I45" s="8" t="n">
         <v>12.8</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>CT2</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n">
+      <c r="C46" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D41" s="12" t="n">
+      <c r="D46" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>1.2</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>29.1</v>
       </c>
-      <c r="H41" s="12" t="n">
+      <c r="H46" s="12" t="n">
         <v>51.2</v>
       </c>
-      <c r="I41" s="12" t="n">
+      <c r="I46" s="12" t="n">
         <v>18.6</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>CT3</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C42" s="8" t="n">
+      <c r="C47" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D42" s="8" t="n">
+      <c r="D47" s="8" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="F47" s="8" t="n">
         <v>3.5</v>
       </c>
-      <c r="G42" s="8" t="n">
+      <c r="G47" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="H42" s="8" t="n">
+      <c r="H47" s="8" t="n">
         <v>46.5</v>
       </c>
-      <c r="I42" s="8" t="n">
+      <c r="I47" s="8" t="n">
         <v>20.9</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>CT4</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C43" s="12" t="n">
+      <c r="C48" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="D48" s="12" t="n">
         <v>64.5</v>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>En desarrollo (ED)</t>
         </is>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>16.3</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>51.2</v>
       </c>
-      <c r="H43" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="I43" s="12" t="n">
+      <c r="I48" s="12" t="n">
         <v>15.1</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="6" t="n"/>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="6" t="n"/>
-      <c r="G45" s="6" t="n"/>
-      <c r="H45" s="6" t="n"/>
-      <c r="I45" s="6" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="6" t="n"/>
+      <c r="I50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>Competencias</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>% Aciertos</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>CAUP0221</t>
         </is>
       </c>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>CE4 / CT2</t>
         </is>
       </c>
-      <c r="I47" s="14" t="n">
+      <c r="I52" s="14" t="n">
         <v>25.6</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t>CAUP0201</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>CE1 / CT1</t>
         </is>
       </c>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
-      <c r="G48" s="16" t="n"/>
-      <c r="H48" s="16" t="n"/>
-      <c r="I48" s="17" t="n">
+      <c r="C53" s="16" t="n"/>
+      <c r="D53" s="16" t="n"/>
+      <c r="E53" s="16" t="n"/>
+      <c r="F53" s="16" t="n"/>
+      <c r="G53" s="16" t="n"/>
+      <c r="H53" s="16" t="n"/>
+      <c r="I53" s="17" t="n">
         <v>30.2</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>CAUP0216</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B54" s="13" t="inlineStr">
         <is>
           <t>CE3 / CT3</t>
         </is>
       </c>
-      <c r="I49" s="14" t="n">
+      <c r="I54" s="14" t="n">
         <v>32.6</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>CAUP0210</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>CE2 / CT4</t>
         </is>
       </c>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="16" t="n"/>
-      <c r="E50" s="16" t="n"/>
-      <c r="F50" s="16" t="n"/>
-      <c r="G50" s="16" t="n"/>
-      <c r="H50" s="16" t="n"/>
-      <c r="I50" s="17" t="n">
+      <c r="C55" s="16" t="n"/>
+      <c r="D55" s="16" t="n"/>
+      <c r="E55" s="16" t="n"/>
+      <c r="F55" s="16" t="n"/>
+      <c r="G55" s="16" t="n"/>
+      <c r="H55" s="16" t="n"/>
+      <c r="I55" s="17" t="n">
         <v>38.4</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="6" t="n"/>
+      <c r="G58" s="6" t="n"/>
+      <c r="H58" s="6" t="n"/>
+      <c r="I58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Competencias</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>CAUP0209</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>CE2 / CT4</t>
+        </is>
+      </c>
+      <c r="I60" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>CAUP0212</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>CE2 / CT1</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="n"/>
+      <c r="D61" s="16" t="n"/>
+      <c r="E61" s="16" t="n"/>
+      <c r="F61" s="16" t="n"/>
+      <c r="G61" s="16" t="n"/>
+      <c r="H61" s="16" t="n"/>
+      <c r="I61" s="19" t="n">
+        <v>98.8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>CAUP0215</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT2</t>
+        </is>
+      </c>
+      <c r="I62" s="18" t="n">
+        <v>98.8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>CAUP0224</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>CE4 / CT2</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="n"/>
+      <c r="D63" s="16" t="n"/>
+      <c r="E63" s="16" t="n"/>
+      <c r="F63" s="16" t="n"/>
+      <c r="G63" s="16" t="n"/>
+      <c r="H63" s="16" t="n"/>
+      <c r="I63" s="19" t="n">
+        <v>98.8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>CAUP0218</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT2</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="n">
+        <v>97.7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>CAUP0222</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>CE4 / CT3</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="n"/>
+      <c r="D65" s="16" t="n"/>
+      <c r="E65" s="16" t="n"/>
+      <c r="F65" s="16" t="n"/>
+      <c r="G65" s="16" t="n"/>
+      <c r="H65" s="16" t="n"/>
+      <c r="I65" s="19" t="n">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>CAUP0211</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>CE2 / CT3</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="n">
+        <v>96.5</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B49:H49"/>
+  <mergeCells count="34">
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B55:H55"/>
     <mergeCell ref="B24:H24"/>
-    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B64:H64"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="B62:H62"/>
     <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B59:H59"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A20:I20"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="A29:I29"/>
     <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B66:H66"/>
     <mergeCell ref="A10:I10"/>
     <mergeCell ref="A28:I28"/>
-    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="B52:H52"/>
     <mergeCell ref="B21:H21"/>
-    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A39:I39"/>
     <mergeCell ref="A34:I34"/>
+    <mergeCell ref="B60:H60"/>
     <mergeCell ref="B23:H23"/>
-    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B29:H29"/>
     <mergeCell ref="H8:I8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2906,7 +3460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3557,563 +4111,701 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Competencias</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>ECOP0120</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>CE2 / CT4</t>
+        </is>
+      </c>
+      <c r="I34" s="18" t="n">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>ECOP0109</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>CE1 / CT3</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="16" t="n"/>
+      <c r="G35" s="16" t="n"/>
+      <c r="H35" s="16" t="n"/>
+      <c r="I35" s="19" t="n">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>ECOP0108</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CT3</t>
+        </is>
+      </c>
+      <c r="I36" s="18" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>══ TA2 — 64 estudiantes ══</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Promedio %</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Nivel</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Mediana %</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Mínimo %</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>Máximo %</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>Desv.</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>% Insuf.</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>% En des.</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>% Satisf./Sobres.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="n">
+    <row r="42">
+      <c r="A42" s="8" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>En desarrollo (ED)</t>
         </is>
       </c>
-      <c r="C35" s="8" t="n">
+      <c r="C42" s="8" t="n">
         <v>65.2</v>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D42" s="8" t="n">
         <v>27.6</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E42" s="8" t="n">
         <v>96.8</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F42" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="G42" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H42" s="8" t="n">
         <v>40.6</v>
       </c>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>35.9 / 4.7</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Distribución (N° estud.):</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>Insuf: 12</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>En des: 26</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>Satisf: 23</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>Sobres: 3</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>Total: 64</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="n"/>
-      <c r="I38" s="6" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="6" t="n"/>
+      <c r="I45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>N° preg.</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>Prom. logro %</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>Nivel</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>% Insuf.</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>% En des.</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>% Satisf.</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>% Sobres.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>CE1</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C40" s="8" t="n">
+      <c r="C47" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="D47" s="8" t="n">
         <v>75.2</v>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F47" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="G40" s="8" t="n">
+      <c r="G47" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="H47" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="I40" s="8" t="n">
+      <c r="I47" s="8" t="n">
         <v>46.9</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>CE2</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n">
+      <c r="C48" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="D41" s="12" t="n">
+      <c r="D48" s="12" t="n">
         <v>52.2</v>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>En desarrollo (ED)</t>
         </is>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>35.9</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>37.5</v>
       </c>
-      <c r="H41" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>18.8</v>
       </c>
-      <c r="I41" s="12" t="n">
+      <c r="I48" s="12" t="n">
         <v>7.8</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>CE3</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C42" s="8" t="n">
+      <c r="C49" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D42" s="8" t="n">
+      <c r="D49" s="8" t="n">
         <v>70.2</v>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="F49" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="G42" s="8" t="n">
+      <c r="G49" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="H42" s="8" t="n">
+      <c r="H49" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="I42" s="8" t="n">
+      <c r="I49" s="8" t="n">
         <v>42.2</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>CT1</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C43" s="12" t="n">
+      <c r="C50" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="D50" s="12" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>En desarrollo (ED)</t>
         </is>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>14.1</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>40.6</v>
       </c>
-      <c r="H43" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>39.1</v>
       </c>
-      <c r="I43" s="12" t="n">
+      <c r="I50" s="12" t="n">
         <v>6.2</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>CT2</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C44" s="8" t="n">
+      <c r="C51" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="D44" s="8" t="n">
+      <c r="D51" s="8" t="n">
         <v>55.7</v>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>En desarrollo (ED)</t>
         </is>
       </c>
-      <c r="F44" s="8" t="n">
+      <c r="F51" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="G44" s="8" t="n">
+      <c r="G51" s="8" t="n">
         <v>45.3</v>
       </c>
-      <c r="H44" s="8" t="n">
+      <c r="H51" s="8" t="n">
         <v>15.6</v>
       </c>
-      <c r="I44" s="8" t="n">
+      <c r="I51" s="8" t="n">
         <v>6.2</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>CT3</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C45" s="12" t="n">
+      <c r="C52" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D45" s="12" t="n">
+      <c r="D52" s="12" t="n">
         <v>48.4</v>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>Insuficiente (I)</t>
         </is>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>21.9</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>59.4</v>
       </c>
-      <c r="H45" s="12" t="n">
+      <c r="H52" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I45" s="12" t="n">
+      <c r="I52" s="12" t="n">
         <v>18.8</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>CT4</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C46" s="8" t="n">
+      <c r="C53" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="8" t="n">
+      <c r="D53" s="8" t="n">
         <v>82.8</v>
       </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F53" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="G46" s="8" t="n">
+      <c r="G53" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H53" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="8" t="n">
+      <c r="I53" s="8" t="n">
         <v>82.8</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="6" t="n"/>
-      <c r="D48" s="6" t="n"/>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="6" t="n"/>
-      <c r="G48" s="6" t="n"/>
-      <c r="H48" s="6" t="n"/>
-      <c r="I48" s="6" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="6" t="n"/>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="6" t="n"/>
+      <c r="I55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Competencias</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="I56" s="7" t="inlineStr">
         <is>
           <t>% Aciertos</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>ECOP0218</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B57" s="13" t="inlineStr">
         <is>
           <t>CE2 / CT1 / CT2</t>
         </is>
       </c>
-      <c r="I50" s="14" t="n">
+      <c r="I57" s="14" t="n">
         <v>4.7</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
         <is>
           <t>ECOP0212</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>CE2 / CT1 / CT2</t>
         </is>
       </c>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
-      <c r="G51" s="16" t="n"/>
-      <c r="H51" s="16" t="n"/>
-      <c r="I51" s="17" t="n">
+      <c r="C58" s="16" t="n"/>
+      <c r="D58" s="16" t="n"/>
+      <c r="E58" s="16" t="n"/>
+      <c r="F58" s="16" t="n"/>
+      <c r="G58" s="16" t="n"/>
+      <c r="H58" s="16" t="n"/>
+      <c r="I58" s="17" t="n">
         <v>12.5</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>ECOP0223</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B59" s="13" t="inlineStr">
         <is>
           <t>CE3 / CT3</t>
         </is>
       </c>
-      <c r="I52" s="14" t="n">
+      <c r="I59" s="14" t="n">
         <v>21.9</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="n"/>
+      <c r="G62" s="6" t="n"/>
+      <c r="H62" s="6" t="n"/>
+      <c r="I62" s="6" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Competencias</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>ECOP0201</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CT1</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="n">
+        <v>90.59999999999999</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="B49:H49"/>
+  <mergeCells count="33">
+    <mergeCell ref="H43:I43"/>
     <mergeCell ref="B24:H24"/>
-    <mergeCell ref="B51:H51"/>
-    <mergeCell ref="B50:H50"/>
-    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="B64:H64"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="B36:H36"/>
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="A5:I5"/>
+    <mergeCell ref="B35:H35"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="H36:I36"/>
     <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B59:H59"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A43:C43"/>
     <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A62:I62"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="B27:H27"/>
     <mergeCell ref="A10:I10"/>
-    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B58:H58"/>
     <mergeCell ref="B21:H21"/>
-    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A39:I39"/>
     <mergeCell ref="B23:H23"/>
-    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="A45:I45"/>
     <mergeCell ref="B29:H29"/>
     <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B34:H34"/>
     <mergeCell ref="B28:H28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4126,7 +4818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4528,360 +5220,207 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Ninguno (ningún ítem por debajo del 50%).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Competencias</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>ECOL0107</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>CE2 / CT3</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>96.09999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>ECOL0110</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>CE2 / CT3</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="16" t="n"/>
+      <c r="I25" s="19" t="n">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>ECOL0116</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CT4</t>
+        </is>
+      </c>
+      <c r="I26" s="18" t="n">
+        <v>94.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>ECOL0106</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>CE2 / CT3</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="16" t="n"/>
+      <c r="G27" s="16" t="n"/>
+      <c r="H27" s="16" t="n"/>
+      <c r="I27" s="19" t="n">
+        <v>92.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>ECOL0114</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CT4</t>
+        </is>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>91.59999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>ECOL0105</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>CE2 / CT3</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
+      <c r="G29" s="16" t="n"/>
+      <c r="H29" s="16" t="n"/>
+      <c r="I29" s="19" t="n">
+        <v>90.90000000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>ECOL0108</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>CE2 / CT3</t>
+        </is>
+      </c>
+      <c r="I30" s="18" t="n">
+        <v>90.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>ECOL0119</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>CE1 / CT4</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
+      <c r="G31" s="16" t="n"/>
+      <c r="H31" s="16" t="n"/>
+      <c r="I31" s="19" t="n">
+        <v>90.3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>══ TA2 — 337 estudiantes ══</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Resultado global de cohorte</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Promedio %</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Nivel</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Mediana %</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Mínimo %</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Máximo %</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>Desv.</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>% Insuf.</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>% En des.</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>% Satisf./Sobres.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Sobresaliente (SO)</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="G25" s="8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>9.8 / 85.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>Distribución (N° estud.):</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Insuf: 2</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>En des: 13</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Satisf: 33</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>Sobres: 289</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Total: 337</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Logro y distribución por competencia</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Código</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>N° preg.</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Prom. logro %</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Nivel</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>% Insuf.</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>% En des.</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>% Satisf.</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>% Sobres.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>CE3</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Específica</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>Sobresaliente (SO)</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>CE4</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>Específica</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="D31" s="12" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>Sobresaliente (SO)</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>81.90000000000001</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>CT1</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>Sobresaliente (SO)</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H32" s="8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I32" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>CT2</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="D33" s="12" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>Sobresaliente (SO)</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G33" s="12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H33" s="12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="I33" s="12" t="n">
-        <v>81.90000000000001</v>
-      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
+          <t>Resultado global de cohorte</t>
         </is>
       </c>
       <c r="B35" s="6" t="n"/>
@@ -4896,43 +5435,736 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
+          <t>Promedio %</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Nivel</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Mediana %</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Mínimo %</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Máximo %</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Desv.</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>% Insuf.</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>% En des.</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>% Satisf./Sobres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Sobresaliente (SO)</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>9.8 / 85.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Distribución (N° estud.):</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Insuf: 2</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>En des: 13</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Satisf: 33</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>Sobres: 289</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Total: 337</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Logro y distribución por competencia</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>N° preg.</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Prom. logro %</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Nivel</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>% Insuf.</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>% En des.</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>% Satisf.</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>% Sobres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>CE3</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Específica</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Sobresaliente (SO)</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>CE4</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Específica</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>Sobresaliente (SO)</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>81.90000000000001</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>CT1</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>Sobresaliente (SO)</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>CT2</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Sobresaliente (SO)</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>81.90000000000001</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n"/>
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="6" t="n"/>
+      <c r="I47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Competencias</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>% Aciertos</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>Ninguno (ningún ítem por debajo del 50%).</t>
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="6" t="n"/>
+      <c r="I52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Competencias</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>ECOL0210</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT1</t>
+        </is>
+      </c>
+      <c r="I54" s="18" t="n">
+        <v>98.8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>ECOL0208</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT1</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="n"/>
+      <c r="D55" s="16" t="n"/>
+      <c r="E55" s="16" t="n"/>
+      <c r="F55" s="16" t="n"/>
+      <c r="G55" s="16" t="n"/>
+      <c r="H55" s="16" t="n"/>
+      <c r="I55" s="19" t="n">
+        <v>98.2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>ECOL0211</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>CE4 / CT2</t>
+        </is>
+      </c>
+      <c r="I56" s="18" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>ECOL0204</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT1</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="n"/>
+      <c r="D57" s="16" t="n"/>
+      <c r="E57" s="16" t="n"/>
+      <c r="F57" s="16" t="n"/>
+      <c r="G57" s="16" t="n"/>
+      <c r="H57" s="16" t="n"/>
+      <c r="I57" s="19" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>ECOL0206</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT1</t>
+        </is>
+      </c>
+      <c r="I58" s="18" t="n">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>ECOL0203</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT1</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="n"/>
+      <c r="D59" s="16" t="n"/>
+      <c r="E59" s="16" t="n"/>
+      <c r="F59" s="16" t="n"/>
+      <c r="G59" s="16" t="n"/>
+      <c r="H59" s="16" t="n"/>
+      <c r="I59" s="19" t="n">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>ECOL0202</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT1</t>
+        </is>
+      </c>
+      <c r="I60" s="18" t="n">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>ECOL0205</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT1</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="n"/>
+      <c r="D61" s="16" t="n"/>
+      <c r="E61" s="16" t="n"/>
+      <c r="F61" s="16" t="n"/>
+      <c r="G61" s="16" t="n"/>
+      <c r="H61" s="16" t="n"/>
+      <c r="I61" s="19" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>ECOL0209</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT1</t>
+        </is>
+      </c>
+      <c r="I62" s="18" t="n">
+        <v>96.40000000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>ECOL0207</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT1</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="n"/>
+      <c r="D63" s="16" t="n"/>
+      <c r="E63" s="16" t="n"/>
+      <c r="F63" s="16" t="n"/>
+      <c r="G63" s="16" t="n"/>
+      <c r="H63" s="16" t="n"/>
+      <c r="I63" s="19" t="n">
+        <v>96.09999999999999</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>ECOL0215</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>CE4 / CT2</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="n">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>ECOL0213</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>CE4 / CT2</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="n"/>
+      <c r="D65" s="16" t="n"/>
+      <c r="E65" s="16" t="n"/>
+      <c r="F65" s="16" t="n"/>
+      <c r="G65" s="16" t="n"/>
+      <c r="H65" s="16" t="n"/>
+      <c r="I65" s="19" t="n">
+        <v>95.3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>ECOL0217</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>CE4 / CT2</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="n">
+        <v>94.09999999999999</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>ECOL0201</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT1</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="n"/>
+      <c r="D67" s="16" t="n"/>
+      <c r="E67" s="16" t="n"/>
+      <c r="F67" s="16" t="n"/>
+      <c r="G67" s="16" t="n"/>
+      <c r="H67" s="16" t="n"/>
+      <c r="I67" s="19" t="n">
+        <v>93.8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>ECOL0218</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>CE4 / CT2</t>
+        </is>
+      </c>
+      <c r="I68" s="18" t="n">
+        <v>93.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>ECOL0214</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>CE4 / CT2</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="n"/>
+      <c r="D69" s="16" t="n"/>
+      <c r="E69" s="16" t="n"/>
+      <c r="F69" s="16" t="n"/>
+      <c r="G69" s="16" t="n"/>
+      <c r="H69" s="16" t="n"/>
+      <c r="I69" s="19" t="n">
+        <v>93.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>ECOL0216</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>CE4 / CT2</t>
+        </is>
+      </c>
+      <c r="I70" s="18" t="n">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B36:H36"/>
+  <mergeCells count="43">
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B68:H68"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B64:H64"/>
+    <mergeCell ref="B63:H63"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="B62:H62"/>
     <mergeCell ref="A22:I22"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="B66:H66"/>
     <mergeCell ref="B18:H18"/>
     <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="B70:H70"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="B60:H60"/>
+    <mergeCell ref="B67:H67"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B29:H29"/>
     <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="B28:H28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4944,7 +6176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5486,551 +6718,1227 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Ninguno (ningún ítem por debajo del 50%).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Competencias</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>TURP0101</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CT4</t>
+        </is>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>TURP0102</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>CE1 / CT4</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
+      <c r="G29" s="16" t="n"/>
+      <c r="H29" s="16" t="n"/>
+      <c r="I29" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>TURP0103</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CT4</t>
+        </is>
+      </c>
+      <c r="I30" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>TURP0104</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>CE1 / CT4</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
+      <c r="G31" s="16" t="n"/>
+      <c r="H31" s="16" t="n"/>
+      <c r="I31" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>TURP0105</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CT4</t>
+        </is>
+      </c>
+      <c r="I32" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>TURP0106</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>CE1 / CT4</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="16" t="n"/>
+      <c r="G33" s="16" t="n"/>
+      <c r="H33" s="16" t="n"/>
+      <c r="I33" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>TURP0107</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>CE2 / CT2</t>
+        </is>
+      </c>
+      <c r="I34" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>TURP0108</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>CE2 / CT2</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="16" t="n"/>
+      <c r="G35" s="16" t="n"/>
+      <c r="H35" s="16" t="n"/>
+      <c r="I35" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>TURP0109</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>CE2 / CT2</t>
+        </is>
+      </c>
+      <c r="I36" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>TURP0110</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>CE2 / CT2</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="16" t="n"/>
+      <c r="H37" s="16" t="n"/>
+      <c r="I37" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>TURP0111</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>CE2 / CT2</t>
+        </is>
+      </c>
+      <c r="I38" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>TURP0112</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>CE2 / CT2</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="16" t="n"/>
+      <c r="G39" s="16" t="n"/>
+      <c r="H39" s="16" t="n"/>
+      <c r="I39" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>TURP0113</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT3</t>
+        </is>
+      </c>
+      <c r="I40" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>TURP0114</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT3</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="16" t="n"/>
+      <c r="G41" s="16" t="n"/>
+      <c r="H41" s="16" t="n"/>
+      <c r="I41" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>TURP0115</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT3</t>
+        </is>
+      </c>
+      <c r="I42" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>TURP0116</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT3</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="16" t="n"/>
+      <c r="G43" s="16" t="n"/>
+      <c r="H43" s="16" t="n"/>
+      <c r="I43" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>TURP0117</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT3</t>
+        </is>
+      </c>
+      <c r="I44" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>TURP0118</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT3</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="16" t="n"/>
+      <c r="E45" s="16" t="n"/>
+      <c r="F45" s="16" t="n"/>
+      <c r="G45" s="16" t="n"/>
+      <c r="H45" s="16" t="n"/>
+      <c r="I45" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>TURP0119</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>CE4 / CT1</t>
+        </is>
+      </c>
+      <c r="I46" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>TURP0120</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>CE4 / CT1</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="n"/>
+      <c r="D47" s="16" t="n"/>
+      <c r="E47" s="16" t="n"/>
+      <c r="F47" s="16" t="n"/>
+      <c r="G47" s="16" t="n"/>
+      <c r="H47" s="16" t="n"/>
+      <c r="I47" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>TURP0121</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>CE4 / CT1</t>
+        </is>
+      </c>
+      <c r="I48" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>TURP0122</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>CE4 / CT1</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="n"/>
+      <c r="D49" s="16" t="n"/>
+      <c r="E49" s="16" t="n"/>
+      <c r="F49" s="16" t="n"/>
+      <c r="G49" s="16" t="n"/>
+      <c r="H49" s="16" t="n"/>
+      <c r="I49" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>TURP0123</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>CE4 / CT1</t>
+        </is>
+      </c>
+      <c r="I50" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>TURP0124</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>CE4 / CT1</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="n"/>
+      <c r="D51" s="16" t="n"/>
+      <c r="E51" s="16" t="n"/>
+      <c r="F51" s="16" t="n"/>
+      <c r="G51" s="16" t="n"/>
+      <c r="H51" s="16" t="n"/>
+      <c r="I51" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>══ TA2 — 19 estudiantes ══</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="6" t="n"/>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="6" t="n"/>
+      <c r="I55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>Promedio %</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Nivel</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Mediana %</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>Mínimo %</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>Máximo %</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>Desv.</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>% Insuf.</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>% En des.</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I56" s="7" t="inlineStr">
         <is>
           <t>% Satisf./Sobres.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
+    <row r="57">
+      <c r="A57" s="8" t="n">
         <v>81.8</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="C29" s="8" t="n">
+      <c r="C57" s="8" t="n">
         <v>79.2</v>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D57" s="8" t="n">
         <v>58.3</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E57" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F57" s="8" t="n">
         <v>11.7</v>
       </c>
-      <c r="G29" s="8" t="n">
+      <c r="G57" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H57" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I57" s="8" t="inlineStr">
         <is>
           <t>47.4 / 36.8</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>Distribución (N° estud.):</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>Insuf: 0</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>En des: 3</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>Satisf: 9</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>Sobres: 7</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H58" s="8" t="inlineStr">
         <is>
           <t>Total: 19</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="6" t="n"/>
+      <c r="G60" s="6" t="n"/>
+      <c r="H60" s="6" t="n"/>
+      <c r="I60" s="6" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>N° preg.</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>Prom. logro %</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>Nivel</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>% Insuf.</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>% En des.</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>% Satisf.</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I61" s="7" t="inlineStr">
         <is>
           <t>% Sobres.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>CE1</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C34" s="8" t="n">
+      <c r="C62" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D62" s="8" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="F62" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G62" s="8" t="n">
         <v>42.1</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H62" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="I34" s="8" t="n">
+      <c r="I62" s="8" t="n">
         <v>15.8</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>CE2</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C35" s="12" t="n">
+      <c r="C63" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="D63" s="12" t="n">
         <v>79.8</v>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F63" s="12" t="n">
         <v>10.5</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G63" s="12" t="n">
         <v>21.1</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="H63" s="12" t="n">
         <v>21.1</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="I63" s="12" t="n">
         <v>47.4</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>CE3</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C36" s="8" t="n">
+      <c r="C64" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D64" s="8" t="n">
         <v>94.7</v>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>Sobresaliente (SO)</t>
         </is>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F64" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G64" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="H64" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="I36" s="8" t="n">
+      <c r="I64" s="8" t="n">
         <v>68.40000000000001</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>CE4</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n">
+      <c r="C65" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D37" s="12" t="n">
+      <c r="D65" s="12" t="n">
         <v>80.7</v>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="F65" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="G65" s="12" t="n">
         <v>36.8</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="H65" s="12" t="n">
         <v>31.6</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="I65" s="12" t="n">
         <v>31.6</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>CT1</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C38" s="8" t="n">
+      <c r="C66" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D66" s="8" t="n">
         <v>80.7</v>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F66" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="8" t="n">
+      <c r="G66" s="8" t="n">
         <v>36.8</v>
       </c>
-      <c r="H38" s="8" t="n">
+      <c r="H66" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="I38" s="8" t="n">
+      <c r="I66" s="8" t="n">
         <v>31.6</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>CT2</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n">
+      <c r="C67" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D67" s="12" t="n">
         <v>79.8</v>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E67" s="12" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="F67" s="12" t="n">
         <v>10.5</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="G67" s="12" t="n">
         <v>21.1</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="H67" s="12" t="n">
         <v>21.1</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="I67" s="12" t="n">
         <v>47.4</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>CT3</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C40" s="8" t="n">
+      <c r="C68" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="D68" s="8" t="n">
         <v>94.7</v>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>Sobresaliente (SO)</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F68" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="8" t="n">
+      <c r="G68" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="H68" s="8" t="n">
         <v>31.6</v>
       </c>
-      <c r="I40" s="8" t="n">
+      <c r="I68" s="8" t="n">
         <v>68.40000000000001</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>CT4</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n">
+      <c r="C69" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D41" s="12" t="n">
+      <c r="D69" s="12" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E69" s="12" t="inlineStr">
         <is>
           <t>Satisfactorio (S)</t>
         </is>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="F69" s="12" t="n">
         <v>10.5</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="G69" s="12" t="n">
         <v>42.1</v>
       </c>
-      <c r="H41" s="12" t="n">
+      <c r="H69" s="12" t="n">
         <v>31.6</v>
       </c>
-      <c r="I41" s="12" t="n">
+      <c r="I69" s="12" t="n">
         <v>15.8</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="6" t="n"/>
-      <c r="H43" s="6" t="n"/>
-      <c r="I43" s="6" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="6" t="n"/>
+      <c r="G71" s="6" t="n"/>
+      <c r="H71" s="6" t="n"/>
+      <c r="I71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>Competencias</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="I72" s="7" t="inlineStr">
         <is>
           <t>% Aciertos</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="20" t="inlineStr">
         <is>
           <t>Ninguno (ningún ítem por debajo del 50%).</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="6" t="n"/>
+      <c r="G76" s="6" t="n"/>
+      <c r="H76" s="6" t="n"/>
+      <c r="I76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Competencias</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>TURP0221</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>CE4 / CT1</t>
+        </is>
+      </c>
+      <c r="I78" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>TURP0218</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT3</t>
+        </is>
+      </c>
+      <c r="C79" s="16" t="n"/>
+      <c r="D79" s="16" t="n"/>
+      <c r="E79" s="16" t="n"/>
+      <c r="F79" s="16" t="n"/>
+      <c r="G79" s="16" t="n"/>
+      <c r="H79" s="16" t="n"/>
+      <c r="I79" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>TURP0216</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT3</t>
+        </is>
+      </c>
+      <c r="I80" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>TURP0211</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>CE2 / CT2</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="n"/>
+      <c r="D81" s="16" t="n"/>
+      <c r="E81" s="16" t="n"/>
+      <c r="F81" s="16" t="n"/>
+      <c r="G81" s="16" t="n"/>
+      <c r="H81" s="16" t="n"/>
+      <c r="I81" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>TURP0215</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT3</t>
+        </is>
+      </c>
+      <c r="I82" s="18" t="n">
+        <v>94.7</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>TURP0214</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT3</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="n"/>
+      <c r="D83" s="16" t="n"/>
+      <c r="E83" s="16" t="n"/>
+      <c r="F83" s="16" t="n"/>
+      <c r="G83" s="16" t="n"/>
+      <c r="H83" s="16" t="n"/>
+      <c r="I83" s="19" t="n">
+        <v>94.7</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>TURP0213</t>
+        </is>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT3</t>
+        </is>
+      </c>
+      <c r="I84" s="18" t="n">
+        <v>94.7</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>TURP0206</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>CE1 / CT4</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="n"/>
+      <c r="D85" s="16" t="n"/>
+      <c r="E85" s="16" t="n"/>
+      <c r="F85" s="16" t="n"/>
+      <c r="G85" s="16" t="n"/>
+      <c r="H85" s="16" t="n"/>
+      <c r="I85" s="19" t="n">
+        <v>94.7</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="B44:H44"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A4:I4"/>
+  <mergeCells count="50">
+    <mergeCell ref="B84:H84"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="A54:I54"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B83:H83"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="B80:H80"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="A21:I21"/>
-    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="B79:H79"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B72:H72"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B81:H81"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B77:H77"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B82:H82"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B78:H78"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B28:H28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6042,7 +7950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6549,551 +8457,1677 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Ninguno (ningún ítem por debajo del 50%).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Competencias</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>TURL0127</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>CT2</t>
+        </is>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>TURL0119</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>CT3</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
+      <c r="G28" s="16" t="n"/>
+      <c r="H28" s="16" t="n"/>
+      <c r="I28" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>TURL0122</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>CT3</t>
+        </is>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>TURL0104</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>CE1 / CT1</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="16" t="n"/>
+      <c r="H30" s="16" t="n"/>
+      <c r="I30" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>TURL0106</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CT3</t>
+        </is>
+      </c>
+      <c r="I31" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>TURL0111</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>CE2 / CT3</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="16" t="n"/>
+      <c r="H32" s="16" t="n"/>
+      <c r="I32" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>TURL0115</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT4</t>
+        </is>
+      </c>
+      <c r="I33" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>TURL0117</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT4</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="16" t="n"/>
+      <c r="F34" s="16" t="n"/>
+      <c r="G34" s="16" t="n"/>
+      <c r="H34" s="16" t="n"/>
+      <c r="I34" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>TURL0101</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CT1</t>
+        </is>
+      </c>
+      <c r="I35" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>TURL0103</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>CE1 / CT1</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
+      <c r="G36" s="16" t="n"/>
+      <c r="H36" s="16" t="n"/>
+      <c r="I36" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>TURL0102</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CT1</t>
+        </is>
+      </c>
+      <c r="I37" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>TURL0113</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT4</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
+      <c r="G38" s="16" t="n"/>
+      <c r="H38" s="16" t="n"/>
+      <c r="I38" s="19" t="n">
+        <v>97.59999999999999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>TURL0114</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT4</t>
+        </is>
+      </c>
+      <c r="I39" s="18" t="n">
+        <v>97.59999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>TURL0110</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>CE2 / CT3</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="16" t="n"/>
+      <c r="G40" s="16" t="n"/>
+      <c r="H40" s="16" t="n"/>
+      <c r="I40" s="19" t="n">
+        <v>97.59999999999999</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>TURL0130</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>CT2</t>
+        </is>
+      </c>
+      <c r="I41" s="18" t="n">
+        <v>97.59999999999999</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>TURL0128</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>CT2</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
+      <c r="G42" s="16" t="n"/>
+      <c r="H42" s="16" t="n"/>
+      <c r="I42" s="19" t="n">
+        <v>97.59999999999999</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>TURL0129</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>CT2</t>
+        </is>
+      </c>
+      <c r="I43" s="18" t="n">
+        <v>97.59999999999999</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>TURL0121</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>CT3</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="16" t="n"/>
+      <c r="G44" s="16" t="n"/>
+      <c r="H44" s="16" t="n"/>
+      <c r="I44" s="19" t="n">
+        <v>95.2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>TURL0118</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT4</t>
+        </is>
+      </c>
+      <c r="I45" s="18" t="n">
+        <v>95.2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>TURL0125</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>CT2</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="n"/>
+      <c r="D46" s="16" t="n"/>
+      <c r="E46" s="16" t="n"/>
+      <c r="F46" s="16" t="n"/>
+      <c r="G46" s="16" t="n"/>
+      <c r="H46" s="16" t="n"/>
+      <c r="I46" s="19" t="n">
+        <v>95.2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>TURL0109</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>CE2 / CT3</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="n">
+        <v>95.2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>TURL0123</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>CT3</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="n"/>
+      <c r="D48" s="16" t="n"/>
+      <c r="E48" s="16" t="n"/>
+      <c r="F48" s="16" t="n"/>
+      <c r="G48" s="16" t="n"/>
+      <c r="H48" s="16" t="n"/>
+      <c r="I48" s="19" t="n">
+        <v>95.2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>TURL0105</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CT1</t>
+        </is>
+      </c>
+      <c r="I49" s="18" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>TURL0120</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>CT3</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="n"/>
+      <c r="D50" s="16" t="n"/>
+      <c r="E50" s="16" t="n"/>
+      <c r="F50" s="16" t="n"/>
+      <c r="G50" s="16" t="n"/>
+      <c r="H50" s="16" t="n"/>
+      <c r="I50" s="19" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>TURL0116</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT4</t>
+        </is>
+      </c>
+      <c r="I51" s="18" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>TURL0112</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>CE2 / CT3</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="n"/>
+      <c r="D52" s="16" t="n"/>
+      <c r="E52" s="16" t="n"/>
+      <c r="F52" s="16" t="n"/>
+      <c r="G52" s="16" t="n"/>
+      <c r="H52" s="16" t="n"/>
+      <c r="I52" s="19" t="n">
+        <v>90.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>TURL0124</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>CT3</t>
+        </is>
+      </c>
+      <c r="I53" s="18" t="n">
+        <v>90.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>══ TA2 — 95 estudiantes ══</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="B56" s="4" t="n"/>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n"/>
+      <c r="F57" s="6" t="n"/>
+      <c r="G57" s="6" t="n"/>
+      <c r="H57" s="6" t="n"/>
+      <c r="I57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>Promedio %</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>Nivel</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>Mediana %</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>Mínimo %</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>Máximo %</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>Desv.</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G58" s="7" t="inlineStr">
         <is>
           <t>% Insuf.</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr">
         <is>
           <t>% En des.</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I58" s="7" t="inlineStr">
         <is>
           <t>% Satisf./Sobres.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="n">
+    <row r="59">
+      <c r="A59" s="8" t="n">
         <v>97.09999999999999</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Sobresaliente (SO)</t>
         </is>
       </c>
-      <c r="C28" s="8" t="n">
+      <c r="C59" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D28" s="8" t="n">
+      <c r="D59" s="8" t="n">
         <v>43.9</v>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="E59" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="F59" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="G28" s="8" t="n">
+      <c r="G59" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H59" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I59" s="8" t="inlineStr">
         <is>
           <t>6.3 / 91.6</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>Distribución (N° estud.):</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>Insuf: 1</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>En des: 1</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>Satisf: 6</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>Sobres: 87</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>Total: 95</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="n"/>
+      <c r="G62" s="6" t="n"/>
+      <c r="H62" s="6" t="n"/>
+      <c r="I62" s="6" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>N° preg.</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>Prom. logro %</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>Nivel</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>% Insuf.</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>% En des.</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H63" s="7" t="inlineStr">
         <is>
           <t>% Satisf.</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I63" s="7" t="inlineStr">
         <is>
           <t>% Sobres.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>CE1</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C33" s="8" t="n">
+      <c r="C64" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D64" s="8" t="n">
         <v>97.5</v>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>Sobresaliente (SO)</t>
         </is>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F64" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G64" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="8" t="n">
+      <c r="H64" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="I33" s="8" t="n">
+      <c r="I64" s="8" t="n">
         <v>86.3</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>CE2</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n">
+      <c r="C65" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="D34" s="12" t="n">
+      <c r="D65" s="12" t="n">
         <v>97.09999999999999</v>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>Sobresaliente (SO)</t>
         </is>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="F65" s="12" t="n">
         <v>1.1</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="G65" s="12" t="n">
         <v>2.1</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="H65" s="12" t="n">
         <v>4.2</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="I65" s="12" t="n">
         <v>92.59999999999999</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>CE3</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C35" s="8" t="n">
+      <c r="C66" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D66" s="8" t="n">
         <v>97.7</v>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>Sobresaliente (SO)</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F66" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="G66" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H66" s="8" t="n">
         <v>8.4</v>
       </c>
-      <c r="I35" s="8" t="n">
+      <c r="I66" s="8" t="n">
         <v>90.5</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>CE4</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>Específica</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n">
+      <c r="C67" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="D36" s="12" t="n">
+      <c r="D67" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E67" s="12" t="inlineStr">
         <is>
           <t>Sobresaliente (SO)</t>
         </is>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="F67" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="G67" s="12" t="n">
         <v>2.1</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="H67" s="12" t="n">
         <v>6.3</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="I67" s="12" t="n">
         <v>91.59999999999999</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>CT1</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C37" s="8" t="n">
+      <c r="C68" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D37" s="8" t="n">
+      <c r="D68" s="8" t="n">
         <v>97.7</v>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>Sobresaliente (SO)</t>
         </is>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="F68" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="G37" s="8" t="n">
+      <c r="G68" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="H37" s="8" t="n">
+      <c r="H68" s="8" t="n">
         <v>7.4</v>
       </c>
-      <c r="I37" s="8" t="n">
+      <c r="I68" s="8" t="n">
         <v>90.5</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>CT2</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="C69" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="D69" s="12" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E69" s="12" t="inlineStr">
         <is>
           <t>Sobresaliente (SO)</t>
         </is>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F69" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="G69" s="12" t="n">
         <v>5.3</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="H69" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="I69" s="12" t="n">
         <v>74.7</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>CT3</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C39" s="8" t="n">
+      <c r="C70" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="D70" s="8" t="n">
         <v>98.3</v>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E70" s="8" t="inlineStr">
         <is>
           <t>Sobresaliente (SO)</t>
         </is>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F70" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G70" s="8" t="n">
         <v>2.1</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H70" s="8" t="n">
         <v>5.3</v>
       </c>
-      <c r="I39" s="8" t="n">
+      <c r="I70" s="8" t="n">
         <v>92.59999999999999</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t>CT4</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n">
+      <c r="C71" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="D40" s="12" t="n">
+      <c r="D71" s="12" t="n">
         <v>97.7</v>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E71" s="12" t="inlineStr">
         <is>
           <t>Sobresaliente (SO)</t>
         </is>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F71" s="12" t="n">
         <v>1.1</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="G71" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="12" t="n">
+      <c r="H71" s="12" t="n">
         <v>8.4</v>
       </c>
-      <c r="I40" s="12" t="n">
+      <c r="I71" s="12" t="n">
         <v>90.5</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n"/>
-      <c r="G42" s="6" t="n"/>
-      <c r="H42" s="6" t="n"/>
-      <c r="I42" s="6" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="6" t="n"/>
+      <c r="G73" s="6" t="n"/>
+      <c r="H73" s="6" t="n"/>
+      <c r="I73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>Competencias</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="I74" s="7" t="inlineStr">
         <is>
           <t>% Aciertos</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="20" t="inlineStr">
         <is>
           <t>Ninguno (ningún ítem por debajo del 50%).</t>
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n"/>
+      <c r="F78" s="6" t="n"/>
+      <c r="G78" s="6" t="n"/>
+      <c r="H78" s="6" t="n"/>
+      <c r="I78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Competencias</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>TURL0229</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CE4</t>
+        </is>
+      </c>
+      <c r="I80" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>TURL0220</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>CT3</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="n"/>
+      <c r="D81" s="16" t="n"/>
+      <c r="E81" s="16" t="n"/>
+      <c r="F81" s="16" t="n"/>
+      <c r="G81" s="16" t="n"/>
+      <c r="H81" s="16" t="n"/>
+      <c r="I81" s="19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>TURL0221</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>CT3</t>
+        </is>
+      </c>
+      <c r="I82" s="18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>TURL0203</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>CT3</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="n"/>
+      <c r="D83" s="16" t="n"/>
+      <c r="E83" s="16" t="n"/>
+      <c r="F83" s="16" t="n"/>
+      <c r="G83" s="16" t="n"/>
+      <c r="H83" s="16" t="n"/>
+      <c r="I83" s="19" t="n">
+        <v>98.90000000000001</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>TURL0205</t>
+        </is>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT4</t>
+        </is>
+      </c>
+      <c r="I84" s="18" t="n">
+        <v>98.90000000000001</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>TURL0217</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT4</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="n"/>
+      <c r="D85" s="16" t="n"/>
+      <c r="E85" s="16" t="n"/>
+      <c r="F85" s="16" t="n"/>
+      <c r="G85" s="16" t="n"/>
+      <c r="H85" s="16" t="n"/>
+      <c r="I85" s="19" t="n">
+        <v>98.90000000000001</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>TURL0216</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>CT1</t>
+        </is>
+      </c>
+      <c r="I86" s="18" t="n">
+        <v>98.90000000000001</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>TURL0204</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>CT3</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="n"/>
+      <c r="D87" s="16" t="n"/>
+      <c r="E87" s="16" t="n"/>
+      <c r="F87" s="16" t="n"/>
+      <c r="G87" s="16" t="n"/>
+      <c r="H87" s="16" t="n"/>
+      <c r="I87" s="19" t="n">
+        <v>98.90000000000001</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>TURL0215</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>CT1</t>
+        </is>
+      </c>
+      <c r="I88" s="18" t="n">
+        <v>98.90000000000001</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>TURL0226</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>CE1 / CE4</t>
+        </is>
+      </c>
+      <c r="C89" s="16" t="n"/>
+      <c r="D89" s="16" t="n"/>
+      <c r="E89" s="16" t="n"/>
+      <c r="F89" s="16" t="n"/>
+      <c r="G89" s="16" t="n"/>
+      <c r="H89" s="16" t="n"/>
+      <c r="I89" s="19" t="n">
+        <v>98.90000000000001</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>TURL0225</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>CE4 / CT2</t>
+        </is>
+      </c>
+      <c r="I90" s="18" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>TURL0228</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>CE1 / CE4</t>
+        </is>
+      </c>
+      <c r="C91" s="16" t="n"/>
+      <c r="D91" s="16" t="n"/>
+      <c r="E91" s="16" t="n"/>
+      <c r="F91" s="16" t="n"/>
+      <c r="G91" s="16" t="n"/>
+      <c r="H91" s="16" t="n"/>
+      <c r="I91" s="19" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>TURL0211</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CT1</t>
+        </is>
+      </c>
+      <c r="I92" s="18" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>TURL0213</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>CE2 / CT3</t>
+        </is>
+      </c>
+      <c r="C93" s="16" t="n"/>
+      <c r="D93" s="16" t="n"/>
+      <c r="E93" s="16" t="n"/>
+      <c r="F93" s="16" t="n"/>
+      <c r="G93" s="16" t="n"/>
+      <c r="H93" s="16" t="n"/>
+      <c r="I93" s="19" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>TURL0201</t>
+        </is>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>CE2 / CT3</t>
+        </is>
+      </c>
+      <c r="I94" s="18" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>TURL0223</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>CE4 / CT2</t>
+        </is>
+      </c>
+      <c r="C95" s="16" t="n"/>
+      <c r="D95" s="16" t="n"/>
+      <c r="E95" s="16" t="n"/>
+      <c r="F95" s="16" t="n"/>
+      <c r="G95" s="16" t="n"/>
+      <c r="H95" s="16" t="n"/>
+      <c r="I95" s="19" t="n">
+        <v>97.90000000000001</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>TURL0207</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CT1</t>
+        </is>
+      </c>
+      <c r="I96" s="18" t="n">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>TURL0210</t>
+        </is>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>CE1 / CT1</t>
+        </is>
+      </c>
+      <c r="C97" s="16" t="n"/>
+      <c r="D97" s="16" t="n"/>
+      <c r="E97" s="16" t="n"/>
+      <c r="F97" s="16" t="n"/>
+      <c r="G97" s="16" t="n"/>
+      <c r="H97" s="16" t="n"/>
+      <c r="I97" s="19" t="n">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>TURL0208</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>CE4 / CT2</t>
+        </is>
+      </c>
+      <c r="I98" s="18" t="n">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>TURL0209</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>CE1 / CT1</t>
+        </is>
+      </c>
+      <c r="C99" s="16" t="n"/>
+      <c r="D99" s="16" t="n"/>
+      <c r="E99" s="16" t="n"/>
+      <c r="F99" s="16" t="n"/>
+      <c r="G99" s="16" t="n"/>
+      <c r="H99" s="16" t="n"/>
+      <c r="I99" s="19" t="n">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>TURL0230</t>
+        </is>
+      </c>
+      <c r="B100" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CE4</t>
+        </is>
+      </c>
+      <c r="I100" s="18" t="n">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>TURL0206</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT4</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="n"/>
+      <c r="D101" s="16" t="n"/>
+      <c r="E101" s="16" t="n"/>
+      <c r="F101" s="16" t="n"/>
+      <c r="G101" s="16" t="n"/>
+      <c r="H101" s="16" t="n"/>
+      <c r="I101" s="19" t="n">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>TURL0219</t>
+        </is>
+      </c>
+      <c r="B102" s="13" t="inlineStr">
+        <is>
+          <t>CE3 / CT4</t>
+        </is>
+      </c>
+      <c r="I102" s="18" t="n">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>TURL0218</t>
+        </is>
+      </c>
+      <c r="B103" s="15" t="inlineStr">
+        <is>
+          <t>CE3 / CT4</t>
+        </is>
+      </c>
+      <c r="C103" s="16" t="n"/>
+      <c r="D103" s="16" t="n"/>
+      <c r="E103" s="16" t="n"/>
+      <c r="F103" s="16" t="n"/>
+      <c r="G103" s="16" t="n"/>
+      <c r="H103" s="16" t="n"/>
+      <c r="I103" s="19" t="n">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>TURL0202</t>
+        </is>
+      </c>
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>CE2 / CT3</t>
+        </is>
+      </c>
+      <c r="I104" s="18" t="n">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>TURL0214</t>
+        </is>
+      </c>
+      <c r="B105" s="15" t="inlineStr">
+        <is>
+          <t>CE4 / CT2</t>
+        </is>
+      </c>
+      <c r="C105" s="16" t="n"/>
+      <c r="D105" s="16" t="n"/>
+      <c r="E105" s="16" t="n"/>
+      <c r="F105" s="16" t="n"/>
+      <c r="G105" s="16" t="n"/>
+      <c r="H105" s="16" t="n"/>
+      <c r="I105" s="19" t="n">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>TURL0227</t>
+        </is>
+      </c>
+      <c r="B106" s="13" t="inlineStr">
+        <is>
+          <t>CE1 / CE4</t>
+        </is>
+      </c>
+      <c r="I106" s="18" t="n">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>TURL0224</t>
+        </is>
+      </c>
+      <c r="B107" s="15" t="inlineStr">
+        <is>
+          <t>CE4 / CT2</t>
+        </is>
+      </c>
+      <c r="C107" s="16" t="n"/>
+      <c r="D107" s="16" t="n"/>
+      <c r="E107" s="16" t="n"/>
+      <c r="F107" s="16" t="n"/>
+      <c r="G107" s="16" t="n"/>
+      <c r="H107" s="16" t="n"/>
+      <c r="I107" s="19" t="n">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>TURL0212</t>
+        </is>
+      </c>
+      <c r="B108" s="13" t="inlineStr">
+        <is>
+          <t>CE2 / CT3</t>
+        </is>
+      </c>
+      <c r="I108" s="18" t="n">
+        <v>95.8</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A26:I26"/>
+  <mergeCells count="74">
+    <mergeCell ref="B99:H99"/>
     <mergeCell ref="A25:I25"/>
+    <mergeCell ref="B84:H84"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B74:H74"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B83:H83"/>
+    <mergeCell ref="B92:H92"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="B95:H95"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B104:H104"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="B80:H80"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B89:H89"/>
+    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="B79:H79"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="B94:H94"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="B97:H97"/>
+    <mergeCell ref="B91:H91"/>
+    <mergeCell ref="B106:H106"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B100:H100"/>
+    <mergeCell ref="B90:H90"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="B81:H81"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B93:H93"/>
+    <mergeCell ref="B27:H27"/>
     <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="B96:H96"/>
+    <mergeCell ref="B52:H52"/>
     <mergeCell ref="B21:H21"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="B102:H102"/>
     <mergeCell ref="B43:H43"/>
-    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="B105:H105"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="B86:H86"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B98:H98"/>
+    <mergeCell ref="B107:H107"/>
+    <mergeCell ref="B101:H101"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="B88:H88"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B82:H82"/>
+    <mergeCell ref="B87:H87"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B29:H29"/>
     <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="B103:H103"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="A78:I78"/>
+    <mergeCell ref="B108:H108"/>
+    <mergeCell ref="B28:H28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Cuadros_oficiales_por_carrera.xlsx
+++ b/data/Cuadros_oficiales_por_carrera.xlsx
@@ -106,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -154,6 +154,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -519,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -528,6 +532,7 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -544,20 +549,13 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>══ TA1 — 240 estudiantes ══</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -565,14 +563,6 @@
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -686,20 +676,13 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -747,6 +730,11 @@
           <t>% Sobres.</t>
         </is>
       </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -782,6 +770,11 @@
       <c r="I12" s="8" t="n">
         <v>20.8</v>
       </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>Diseña proyectos empresariales mediante análisis cuantitativo y metodologías de gestión, modelando escenarios organizacionales y asignando recursos, con rigor técnico, cumplimiento de objetivos y eficiencia operativa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -817,6 +810,11 @@
       <c r="I13" s="12" t="n">
         <v>5.8</v>
       </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>Analiza mercados y entornos competitivos para estructurar estrategias de posicionamiento empresarial, utilizando segmentación y estudios de demanda, con diferenciación estratégica y generación de ventaja competitiva medible.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -852,6 +850,11 @@
       <c r="I14" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>Evalúa alternativas financieras y estructuras de inversión en organizaciones productivas o de servicios, aplicando herramientas de análisis económico y proyecciones financieras, con sustento cuantitativo, precisión técnica y control del riesgo.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -887,6 +890,11 @@
       <c r="I15" s="12" t="n">
         <v>21.2</v>
       </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>Formula estrategias y modelos de desarrollo empresarial en organizaciones públicas o privadas, con coherencia sistémica, visión directiva, capacidad de liderazgo estratégico y orientación a resultados verificables.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -922,6 +930,11 @@
       <c r="I16" s="8" t="n">
         <v>20.8</v>
       </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>Analiza problemas del contexto profesional y social, a partir de información pertinente, para proponer soluciones fundamentadas, viables y contextualizadas.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -957,6 +970,11 @@
       <c r="I17" s="12" t="n">
         <v>5.8</v>
       </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>Gestiona su aprendizaje de manera autónoma para actualizar sus conocimientos y adaptar su desempeño a los cambios del entorno.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -992,6 +1010,11 @@
       <c r="I18" s="8" t="n">
         <v>20</v>
       </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>Utiliza tecnologías, datos y entornos digitales de manera crítica, segura y pertinente para gestionar información, interactuar responsablemente y generar soluciones de valor.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -1027,21 +1050,19 @@
       <c r="I19" s="12" t="n">
         <v>21.2</v>
       </c>
-    </row>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>Comunica ideas, argumentos y resultados de manera clara, estructurada y pertinente, para facilitar la comprensión, la colaboración y la toma de decisiones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -1086,12 +1107,6 @@
           <t>CE2 / CT2</t>
         </is>
       </c>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
-      <c r="G24" s="16" t="n"/>
-      <c r="H24" s="16" t="n"/>
       <c r="I24" s="17" t="n">
         <v>38.3</v>
       </c>
@@ -1122,30 +1137,18 @@
           <t>CE4 / CT4</t>
         </is>
       </c>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
-      <c r="G26" s="16" t="n"/>
-      <c r="H26" s="16" t="n"/>
       <c r="I26" s="17" t="n">
         <v>46.7</v>
       </c>
     </row>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -1190,12 +1193,6 @@
           <t>CE4 / CT4</t>
         </is>
       </c>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
-      <c r="G32" s="16" t="n"/>
-      <c r="H32" s="16" t="n"/>
       <c r="I32" s="19" t="n">
         <v>95</v>
       </c>
@@ -1215,20 +1212,14 @@
         <v>91.2</v>
       </c>
     </row>
+    <row r="34"/>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
           <t>══ TA2 — 63 estudiantes ══</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -1236,14 +1227,6 @@
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -1357,20 +1340,13 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n"/>
-      <c r="G42" s="6" t="n"/>
-      <c r="H42" s="6" t="n"/>
-      <c r="I42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -1418,6 +1394,11 @@
           <t>% Sobres.</t>
         </is>
       </c>
+      <c r="J43" s="21" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
@@ -1453,6 +1434,11 @@
       <c r="I44" s="8" t="n">
         <v>3.2</v>
       </c>
+      <c r="J44" s="22" t="inlineStr">
+        <is>
+          <t>Diseña proyectos empresariales mediante análisis cuantitativo y metodologías de gestión, modelando escenarios organizacionales y asignando recursos, con rigor técnico, cumplimiento de objetivos y eficiencia operativa.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -1488,6 +1474,11 @@
       <c r="I45" s="12" t="n">
         <v>60.3</v>
       </c>
+      <c r="J45" s="22" t="inlineStr">
+        <is>
+          <t>Analiza mercados y entornos competitivos para estructurar estrategias de posicionamiento empresarial, utilizando segmentación y estudios de demanda, con diferenciación estratégica y generación de ventaja competitiva medible.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
@@ -1523,6 +1514,11 @@
       <c r="I46" s="8" t="n">
         <v>47.6</v>
       </c>
+      <c r="J46" s="22" t="inlineStr">
+        <is>
+          <t>Evalúa alternativas financieras y estructuras de inversión en organizaciones productivas o de servicios, aplicando herramientas de análisis económico y proyecciones financieras, con sustento cuantitativo, precisión técnica y control del riesgo.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -1558,6 +1554,11 @@
       <c r="I47" s="12" t="n">
         <v>46</v>
       </c>
+      <c r="J47" s="22" t="inlineStr">
+        <is>
+          <t>Formula estrategias y modelos de desarrollo empresarial en organizaciones públicas o privadas, con coherencia sistémica, visión directiva, capacidad de liderazgo estratégico y orientación a resultados verificables.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
@@ -1593,6 +1594,11 @@
       <c r="I48" s="8" t="n">
         <v>3.2</v>
       </c>
+      <c r="J48" s="22" t="inlineStr">
+        <is>
+          <t>Analiza problemas del contexto profesional y social, a partir de información pertinente, para proponer soluciones fundamentadas, viables y contextualizadas.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -1628,6 +1634,11 @@
       <c r="I49" s="12" t="n">
         <v>60.3</v>
       </c>
+      <c r="J49" s="22" t="inlineStr">
+        <is>
+          <t>Gestiona su aprendizaje de manera autónoma para actualizar sus conocimientos y adaptar su desempeño a los cambios del entorno.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
@@ -1663,6 +1674,11 @@
       <c r="I50" s="8" t="n">
         <v>47.6</v>
       </c>
+      <c r="J50" s="22" t="inlineStr">
+        <is>
+          <t>Utiliza tecnologías, datos y entornos digitales de manera crítica, segura y pertinente para gestionar información, interactuar responsablemente y generar soluciones de valor.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -1698,21 +1714,19 @@
       <c r="I51" s="12" t="n">
         <v>46</v>
       </c>
-    </row>
+      <c r="J51" s="22" t="inlineStr">
+        <is>
+          <t>Comunica ideas, argumentos y resultados de manera clara, estructurada y pertinente, para facilitar la comprensión, la colaboración y la toma de decisiones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="6" t="n"/>
-      <c r="F53" s="6" t="n"/>
-      <c r="G53" s="6" t="n"/>
-      <c r="H53" s="6" t="n"/>
-      <c r="I53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
@@ -1757,30 +1771,18 @@
           <t>CE1 / CT1</t>
         </is>
       </c>
-      <c r="C56" s="16" t="n"/>
-      <c r="D56" s="16" t="n"/>
-      <c r="E56" s="16" t="n"/>
-      <c r="F56" s="16" t="n"/>
-      <c r="G56" s="16" t="n"/>
-      <c r="H56" s="16" t="n"/>
       <c r="I56" s="17" t="n">
         <v>31.7</v>
       </c>
     </row>
+    <row r="57"/>
+    <row r="58"/>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
           <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
         </is>
       </c>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="6" t="n"/>
-      <c r="G59" s="6" t="n"/>
-      <c r="H59" s="6" t="n"/>
-      <c r="I59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
@@ -1825,12 +1827,6 @@
           <t>CE2 / CT2</t>
         </is>
       </c>
-      <c r="C62" s="16" t="n"/>
-      <c r="D62" s="16" t="n"/>
-      <c r="E62" s="16" t="n"/>
-      <c r="F62" s="16" t="n"/>
-      <c r="G62" s="16" t="n"/>
-      <c r="H62" s="16" t="n"/>
       <c r="I62" s="19" t="n">
         <v>95.2</v>
       </c>
@@ -1861,12 +1857,6 @@
           <t>CE2 / CT2</t>
         </is>
       </c>
-      <c r="C64" s="16" t="n"/>
-      <c r="D64" s="16" t="n"/>
-      <c r="E64" s="16" t="n"/>
-      <c r="F64" s="16" t="n"/>
-      <c r="G64" s="16" t="n"/>
-      <c r="H64" s="16" t="n"/>
       <c r="I64" s="19" t="n">
         <v>93.7</v>
       </c>
@@ -1897,12 +1887,6 @@
           <t>CE4 / CT4</t>
         </is>
       </c>
-      <c r="C66" s="16" t="n"/>
-      <c r="D66" s="16" t="n"/>
-      <c r="E66" s="16" t="n"/>
-      <c r="F66" s="16" t="n"/>
-      <c r="G66" s="16" t="n"/>
-      <c r="H66" s="16" t="n"/>
       <c r="I66" s="19" t="n">
         <v>92.09999999999999</v>
       </c>
@@ -1933,12 +1917,6 @@
           <t>CE4 / CT4</t>
         </is>
       </c>
-      <c r="C68" s="16" t="n"/>
-      <c r="D68" s="16" t="n"/>
-      <c r="E68" s="16" t="n"/>
-      <c r="F68" s="16" t="n"/>
-      <c r="G68" s="16" t="n"/>
-      <c r="H68" s="16" t="n"/>
       <c r="I68" s="19" t="n">
         <v>90.5</v>
       </c>
@@ -1969,12 +1947,6 @@
           <t>CE1 / CT1</t>
         </is>
       </c>
-      <c r="C70" s="16" t="n"/>
-      <c r="D70" s="16" t="n"/>
-      <c r="E70" s="16" t="n"/>
-      <c r="F70" s="16" t="n"/>
-      <c r="G70" s="16" t="n"/>
-      <c r="H70" s="16" t="n"/>
       <c r="I70" s="19" t="n">
         <v>90.5</v>
       </c>
@@ -1997,8 +1969,8 @@
   </sheetData>
   <mergeCells count="38">
     <mergeCell ref="A37:I37"/>
+    <mergeCell ref="B68:H68"/>
     <mergeCell ref="B65:H65"/>
-    <mergeCell ref="B68:H68"/>
     <mergeCell ref="B55:H55"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="B30:H30"/>
@@ -2045,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2026,7 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2070,20 +2043,13 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>══ TA1 — 135 estudiantes ══</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -2091,14 +2057,6 @@
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2212,20 +2170,13 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -2273,6 +2224,11 @@
           <t>% Sobres.</t>
         </is>
       </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -2308,6 +2264,11 @@
       <c r="I12" s="8" t="n">
         <v>8.9</v>
       </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>Registra operaciones económicas de una entidad para la elaboración de estados financieros orientados a la toma de decisiones conforme a la normativa contable.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -2343,6 +2304,11 @@
       <c r="I13" s="12" t="n">
         <v>14.8</v>
       </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>Calcula las obligaciones tributarias de personas naturales y jurídicas con base a la legislación tributaria garantizando la exactitud de las declaraciones.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -2378,6 +2344,11 @@
       <c r="I14" s="8" t="n">
         <v>9.6</v>
       </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>Gestiona los recursos financieros de las organizaciones, garantizando la adecuada planificación y control financiero.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -2413,6 +2384,11 @@
       <c r="I15" s="12" t="n">
         <v>14.8</v>
       </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>Analiza situaciones profesionales y toma decisiones fundamentadas considerando impactos sociales, ambientales, económicos y tecnológicos, actuando con responsabilidad, integridad y compromiso con el desarrollo sostenible en contextos locales y globales.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -2448,6 +2424,11 @@
       <c r="I16" s="8" t="n">
         <v>21.5</v>
       </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>Comunica ideas con claridad y sustento técnico, y colabora eficazmente en equipos diversos e interdisciplinarios, contribuyendo activamente a la construcción de soluciones en entornos profesionales, multiculturales y digitales.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -2483,6 +2464,11 @@
       <c r="I17" s="12" t="n">
         <v>25.9</v>
       </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>Gestiona información y conocimiento con rigor metodológico, actualizándose de manera autónoma y aplicando nuevos saberes para resolver problemas complejos en contextos dinámicos y cambiantes.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -2518,21 +2504,19 @@
       <c r="I18" s="8" t="n">
         <v>11.9</v>
       </c>
-    </row>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>Integra tecnologías digitales, análisis de datos y herramientas emergentes de manera crítica, ética y estratégica para generar soluciones pertinentes y sostenibles en contextos profesionales y sociales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -2577,12 +2561,6 @@
           <t>CE1 / CT1</t>
         </is>
       </c>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="16" t="n"/>
-      <c r="G23" s="16" t="n"/>
-      <c r="H23" s="16" t="n"/>
       <c r="I23" s="17" t="n">
         <v>40</v>
       </c>
@@ -2613,30 +2591,18 @@
           <t>CE2 / CT3</t>
         </is>
       </c>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
-      <c r="G25" s="16" t="n"/>
-      <c r="H25" s="16" t="n"/>
       <c r="I25" s="17" t="n">
         <v>45.9</v>
       </c>
     </row>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -2670,20 +2636,14 @@
         <v>94.8</v>
       </c>
     </row>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
           <t>══ TA2 — 86 estudiantes ══</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -2691,14 +2651,6 @@
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="n"/>
-      <c r="G34" s="6" t="n"/>
-      <c r="H34" s="6" t="n"/>
-      <c r="I34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -2812,20 +2764,13 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="6" t="n"/>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="6" t="n"/>
-      <c r="G39" s="6" t="n"/>
-      <c r="H39" s="6" t="n"/>
-      <c r="I39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -2873,6 +2818,11 @@
           <t>% Sobres.</t>
         </is>
       </c>
+      <c r="J40" s="21" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
@@ -2908,6 +2858,11 @@
       <c r="I41" s="8" t="n">
         <v>11.6</v>
       </c>
+      <c r="J41" s="22" t="inlineStr">
+        <is>
+          <t>Registra operaciones económicas de una entidad para la elaboración de estados financieros orientados a la toma de decisiones conforme a la normativa contable.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -2943,6 +2898,11 @@
       <c r="I42" s="12" t="n">
         <v>22.1</v>
       </c>
+      <c r="J42" s="22" t="inlineStr">
+        <is>
+          <t>Calcula las obligaciones tributarias de personas naturales y jurídicas con base a la legislación tributaria garantizando la exactitud de las declaraciones.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
@@ -2978,6 +2938,11 @@
       <c r="I43" s="8" t="n">
         <v>17.4</v>
       </c>
+      <c r="J43" s="22" t="inlineStr">
+        <is>
+          <t>Aplica procedimientos de auditoría en el ámbito empresarial para evaluar el control interno y verificar la transparencia de la información financiera, conforme a normas internacionales de auditoría.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -3013,6 +2978,11 @@
       <c r="I44" s="12" t="n">
         <v>18.6</v>
       </c>
+      <c r="J44" s="22" t="inlineStr">
+        <is>
+          <t>Gestiona los recursos financieros de las organizaciones, garantizando la adecuada planificación y control financiero.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
@@ -3048,6 +3018,11 @@
       <c r="I45" s="8" t="n">
         <v>12.8</v>
       </c>
+      <c r="J45" s="22" t="inlineStr">
+        <is>
+          <t>Analiza situaciones profesionales y toma decisiones fundamentadas considerando impactos sociales, ambientales, económicos y tecnológicos, actuando con responsabilidad, integridad y compromiso con el desarrollo sostenible en contextos locales y globales.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -3083,6 +3058,11 @@
       <c r="I46" s="12" t="n">
         <v>18.6</v>
       </c>
+      <c r="J46" s="22" t="inlineStr">
+        <is>
+          <t>Comunica ideas con claridad y sustento técnico, y colabora eficazmente en equipos diversos e interdisciplinarios, contribuyendo activamente a la construcción de soluciones en entornos profesionales, multiculturales y digitales.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
@@ -3118,6 +3098,11 @@
       <c r="I47" s="8" t="n">
         <v>20.9</v>
       </c>
+      <c r="J47" s="22" t="inlineStr">
+        <is>
+          <t>Gestiona información y conocimiento con rigor metodológico, actualizándose de manera autónoma y aplicando nuevos saberes para resolver problemas complejos en contextos dinámicos y cambiantes.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -3153,21 +3138,19 @@
       <c r="I48" s="12" t="n">
         <v>15.1</v>
       </c>
-    </row>
+      <c r="J48" s="22" t="inlineStr">
+        <is>
+          <t>Integra tecnologías digitales, análisis de datos y herramientas emergentes de manera crítica, ética y estratégica para generar soluciones pertinentes y sostenibles en contextos profesionales y sociales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="6" t="n"/>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="6" t="n"/>
-      <c r="I50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -3212,12 +3195,6 @@
           <t>CE1 / CT1</t>
         </is>
       </c>
-      <c r="C53" s="16" t="n"/>
-      <c r="D53" s="16" t="n"/>
-      <c r="E53" s="16" t="n"/>
-      <c r="F53" s="16" t="n"/>
-      <c r="G53" s="16" t="n"/>
-      <c r="H53" s="16" t="n"/>
       <c r="I53" s="17" t="n">
         <v>30.2</v>
       </c>
@@ -3248,30 +3225,18 @@
           <t>CE2 / CT4</t>
         </is>
       </c>
-      <c r="C55" s="16" t="n"/>
-      <c r="D55" s="16" t="n"/>
-      <c r="E55" s="16" t="n"/>
-      <c r="F55" s="16" t="n"/>
-      <c r="G55" s="16" t="n"/>
-      <c r="H55" s="16" t="n"/>
       <c r="I55" s="17" t="n">
         <v>38.4</v>
       </c>
     </row>
+    <row r="56"/>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
           <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
         </is>
       </c>
-      <c r="B58" s="6" t="n"/>
-      <c r="C58" s="6" t="n"/>
-      <c r="D58" s="6" t="n"/>
-      <c r="E58" s="6" t="n"/>
-      <c r="F58" s="6" t="n"/>
-      <c r="G58" s="6" t="n"/>
-      <c r="H58" s="6" t="n"/>
-      <c r="I58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -3316,12 +3281,6 @@
           <t>CE2 / CT1</t>
         </is>
       </c>
-      <c r="C61" s="16" t="n"/>
-      <c r="D61" s="16" t="n"/>
-      <c r="E61" s="16" t="n"/>
-      <c r="F61" s="16" t="n"/>
-      <c r="G61" s="16" t="n"/>
-      <c r="H61" s="16" t="n"/>
       <c r="I61" s="19" t="n">
         <v>98.8</v>
       </c>
@@ -3352,12 +3311,6 @@
           <t>CE4 / CT2</t>
         </is>
       </c>
-      <c r="C63" s="16" t="n"/>
-      <c r="D63" s="16" t="n"/>
-      <c r="E63" s="16" t="n"/>
-      <c r="F63" s="16" t="n"/>
-      <c r="G63" s="16" t="n"/>
-      <c r="H63" s="16" t="n"/>
       <c r="I63" s="19" t="n">
         <v>98.8</v>
       </c>
@@ -3388,12 +3341,6 @@
           <t>CE4 / CT3</t>
         </is>
       </c>
-      <c r="C65" s="16" t="n"/>
-      <c r="D65" s="16" t="n"/>
-      <c r="E65" s="16" t="n"/>
-      <c r="F65" s="16" t="n"/>
-      <c r="G65" s="16" t="n"/>
-      <c r="H65" s="16" t="n"/>
       <c r="I65" s="19" t="n">
         <v>96.5</v>
       </c>
@@ -3460,7 +3407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3469,6 +3416,7 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3485,20 +3433,13 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>══ TA1 — 120 estudiantes ══</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -3506,14 +3447,6 @@
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -3627,20 +3560,13 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -3688,6 +3614,11 @@
           <t>% Sobres.</t>
         </is>
       </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -3723,6 +3654,11 @@
       <c r="I12" s="8" t="n">
         <v>56.7</v>
       </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>Analiza fenómenos económicos mediante el estudio del comportamiento de agentes y la dinámica de variables agregadas, con fundamento en los principios teóricos y metodológicos de la ciencia económica.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -3758,6 +3694,11 @@
       <c r="I13" s="12" t="n">
         <v>0.8</v>
       </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>Construye modelos econométricos a partir de datos económicos, con rigor metodológico, capacidad explicativa y predictiva.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -3793,6 +3734,11 @@
       <c r="I14" s="8" t="n">
         <v>11.7</v>
       </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>Evalúa el desempeño económico y financiero de organizaciones y sectores productivos a través de herramientas e indicadores financieros, con precisión técnica y visión integral.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -3828,6 +3774,11 @@
       <c r="I15" s="12" t="n">
         <v>16.7</v>
       </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>Analiza problemas del contexto profesional y social, a partir de información pertinente, para proponer soluciones fundamentadas, viables y contextualizadas.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -3863,6 +3814,11 @@
       <c r="I16" s="8" t="n">
         <v>0.8</v>
       </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>Gestiona su aprendizaje de manera autónoma para actualizar sus conocimientos y adaptar su desempeño a los cambios del entorno.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -3898,6 +3854,11 @@
       <c r="I17" s="12" t="n">
         <v>27.5</v>
       </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>Comunica ideas, argumentos y resultados de manera clara, estructurada y pertinente, para facilitar la comprensión, la colaboración y la toma de decisiones.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -3933,21 +3894,19 @@
       <c r="I18" s="8" t="n">
         <v>4.2</v>
       </c>
-    </row>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>Utiliza tecnologías, datos y entornos digitales de manera crítica, segura y pertinente para gestionar información, interactuar responsablemente y generar soluciones de valor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -3992,12 +3951,6 @@
           <t>CE2 / CT2</t>
         </is>
       </c>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="16" t="n"/>
-      <c r="G23" s="16" t="n"/>
-      <c r="H23" s="16" t="n"/>
       <c r="I23" s="17" t="n">
         <v>15</v>
       </c>
@@ -4028,12 +3981,6 @@
           <t>CE3 / CT4</t>
         </is>
       </c>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
-      <c r="G25" s="16" t="n"/>
-      <c r="H25" s="16" t="n"/>
       <c r="I25" s="17" t="n">
         <v>19.2</v>
       </c>
@@ -4064,12 +4011,6 @@
           <t>CE3 / CT4</t>
         </is>
       </c>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
-      <c r="G27" s="16" t="n"/>
-      <c r="H27" s="16" t="n"/>
       <c r="I27" s="17" t="n">
         <v>34.2</v>
       </c>
@@ -4100,30 +4041,18 @@
           <t>CE3 / CT1</t>
         </is>
       </c>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
-      <c r="G29" s="16" t="n"/>
-      <c r="H29" s="16" t="n"/>
       <c r="I29" s="17" t="n">
         <v>47.5</v>
       </c>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -4168,12 +4097,6 @@
           <t>CE1 / CT3</t>
         </is>
       </c>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
-      <c r="G35" s="16" t="n"/>
-      <c r="H35" s="16" t="n"/>
       <c r="I35" s="19" t="n">
         <v>91.7</v>
       </c>
@@ -4193,20 +4116,14 @@
         <v>90</v>
       </c>
     </row>
+    <row r="37"/>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
           <t>══ TA2 — 64 estudiantes ══</t>
         </is>
       </c>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -4214,14 +4131,6 @@
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
-      <c r="G40" s="6" t="n"/>
-      <c r="H40" s="6" t="n"/>
-      <c r="I40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -4335,20 +4244,13 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="6" t="n"/>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="6" t="n"/>
-      <c r="G45" s="6" t="n"/>
-      <c r="H45" s="6" t="n"/>
-      <c r="I45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -4396,6 +4298,11 @@
           <t>% Sobres.</t>
         </is>
       </c>
+      <c r="J46" s="21" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
@@ -4431,6 +4338,11 @@
       <c r="I47" s="8" t="n">
         <v>46.9</v>
       </c>
+      <c r="J47" s="22" t="inlineStr">
+        <is>
+          <t>Analiza fenómenos económicos mediante el estudio del comportamiento de agentes y la dinámica de variables agregadas, con fundamento en los principios teóricos y metodológicos de la ciencia económica.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -4466,6 +4378,11 @@
       <c r="I48" s="12" t="n">
         <v>7.8</v>
       </c>
+      <c r="J48" s="22" t="inlineStr">
+        <is>
+          <t>Construye modelos econométricos a partir de datos económicos, con rigor metodológico, capacidad explicativa y predictiva.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
@@ -4501,6 +4418,11 @@
       <c r="I49" s="8" t="n">
         <v>42.2</v>
       </c>
+      <c r="J49" s="22" t="inlineStr">
+        <is>
+          <t>Evalúa el desempeño económico y financiero de organizaciones y sectores productivos a través de herramientas e indicadores financieros, con precisión técnica y visión integral.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -4536,6 +4458,11 @@
       <c r="I50" s="12" t="n">
         <v>6.2</v>
       </c>
+      <c r="J50" s="22" t="inlineStr">
+        <is>
+          <t>Analiza problemas del contexto profesional y social, a partir de información pertinente, para proponer soluciones fundamentadas, viables y contextualizadas.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
@@ -4571,6 +4498,11 @@
       <c r="I51" s="8" t="n">
         <v>6.2</v>
       </c>
+      <c r="J51" s="22" t="inlineStr">
+        <is>
+          <t>Gestiona su aprendizaje de manera autónoma para actualizar sus conocimientos y adaptar su desempeño a los cambios del entorno.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -4606,6 +4538,11 @@
       <c r="I52" s="12" t="n">
         <v>18.8</v>
       </c>
+      <c r="J52" s="22" t="inlineStr">
+        <is>
+          <t>Comunica ideas, argumentos y resultados de manera clara, estructurada y pertinente, para facilitar la comprensión, la colaboración y la toma de decisiones.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
@@ -4641,21 +4578,19 @@
       <c r="I53" s="8" t="n">
         <v>82.8</v>
       </c>
-    </row>
+      <c r="J53" s="22" t="inlineStr">
+        <is>
+          <t>Utiliza tecnologías, datos y entornos digitales de manera crítica, segura y pertinente para gestionar información, interactuar responsablemente y generar soluciones de valor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B55" s="6" t="n"/>
-      <c r="C55" s="6" t="n"/>
-      <c r="D55" s="6" t="n"/>
-      <c r="E55" s="6" t="n"/>
-      <c r="F55" s="6" t="n"/>
-      <c r="G55" s="6" t="n"/>
-      <c r="H55" s="6" t="n"/>
-      <c r="I55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -4700,12 +4635,6 @@
           <t>CE2 / CT1 / CT2</t>
         </is>
       </c>
-      <c r="C58" s="16" t="n"/>
-      <c r="D58" s="16" t="n"/>
-      <c r="E58" s="16" t="n"/>
-      <c r="F58" s="16" t="n"/>
-      <c r="G58" s="16" t="n"/>
-      <c r="H58" s="16" t="n"/>
       <c r="I58" s="17" t="n">
         <v>12.5</v>
       </c>
@@ -4725,20 +4654,14 @@
         <v>21.9</v>
       </c>
     </row>
+    <row r="60"/>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
           <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
         </is>
       </c>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="6" t="n"/>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="6" t="n"/>
-      <c r="F62" s="6" t="n"/>
-      <c r="G62" s="6" t="n"/>
-      <c r="H62" s="6" t="n"/>
-      <c r="I62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -4790,8 +4713,8 @@
     <mergeCell ref="B59:H59"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A62:I62"/>
     <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A62:I62"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="B27:H27"/>
     <mergeCell ref="A10:I10"/>
@@ -4818,7 +4741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4827,6 +4750,7 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4843,20 +4767,13 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>══ TA1 — 154 estudiantes ══</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -4864,14 +4781,6 @@
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -4985,20 +4894,13 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -5046,6 +4948,11 @@
           <t>% Sobres.</t>
         </is>
       </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -5081,6 +4988,11 @@
       <c r="I12" s="8" t="n">
         <v>61</v>
       </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>Analiza fenómenos, modelos e información económica, para comprender la interacción entre los agentes económicos, bajo el criterio de eficiencia.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -5116,6 +5028,11 @@
       <c r="I13" s="12" t="n">
         <v>61</v>
       </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>Aplica herramientas cuantitativas, estadísticas y econométricas para construir escenarios económicos sustentados en la teoría económica, que apoyen la toma de decisiones en contextos de incertidumbre.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -5151,6 +5068,11 @@
       <c r="I14" s="8" t="n">
         <v>61</v>
       </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>Comunica ideas, argumentos y resultados de manera clara, estructurada y pertinente, para facilitar la comprensión, la colaboración y la toma de decisiones.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -5186,21 +5108,19 @@
       <c r="I15" s="12" t="n">
         <v>61</v>
       </c>
-    </row>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>Utiliza tecnologías, datos y entornos digitales de manera crítica, segura y pertinente para gestionar información, interactuar responsablemente y generar soluciones de valor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -5226,20 +5146,14 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -5284,12 +5198,6 @@
           <t>CE2 / CT3</t>
         </is>
       </c>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
-      <c r="G25" s="16" t="n"/>
-      <c r="H25" s="16" t="n"/>
       <c r="I25" s="19" t="n">
         <v>95.5</v>
       </c>
@@ -5320,12 +5228,6 @@
           <t>CE2 / CT3</t>
         </is>
       </c>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
-      <c r="G27" s="16" t="n"/>
-      <c r="H27" s="16" t="n"/>
       <c r="I27" s="19" t="n">
         <v>92.2</v>
       </c>
@@ -5356,12 +5258,6 @@
           <t>CE2 / CT3</t>
         </is>
       </c>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
-      <c r="G29" s="16" t="n"/>
-      <c r="H29" s="16" t="n"/>
       <c r="I29" s="19" t="n">
         <v>90.90000000000001</v>
       </c>
@@ -5392,30 +5288,18 @@
           <t>CE1 / CT4</t>
         </is>
       </c>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
-      <c r="G31" s="16" t="n"/>
-      <c r="H31" s="16" t="n"/>
       <c r="I31" s="19" t="n">
         <v>90.3</v>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
           <t>══ TA2 — 337 estudiantes ══</t>
         </is>
       </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -5423,14 +5307,6 @@
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="n"/>
-      <c r="I35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -5544,20 +5420,13 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
-      <c r="G40" s="6" t="n"/>
-      <c r="H40" s="6" t="n"/>
-      <c r="I40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -5605,6 +5474,11 @@
           <t>% Sobres.</t>
         </is>
       </c>
+      <c r="J41" s="21" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
@@ -5640,6 +5514,11 @@
       <c r="I42" s="8" t="n">
         <v>92.90000000000001</v>
       </c>
+      <c r="J42" s="22" t="inlineStr">
+        <is>
+          <t>Evalúa políticas públicas, planes, programas y proyectos económicos para proponer soluciones a problemáticas económicas, considerando los sectores público y privado.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -5675,6 +5554,11 @@
       <c r="I43" s="12" t="n">
         <v>81.90000000000001</v>
       </c>
+      <c r="J43" s="22" t="inlineStr">
+        <is>
+          <t>Desarrolla investigación económica aplicada para proponer soluciones a problemas económicos y sociales vinculados al entorno local y global.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
@@ -5710,6 +5594,11 @@
       <c r="I44" s="8" t="n">
         <v>92.90000000000001</v>
       </c>
+      <c r="J44" s="22" t="inlineStr">
+        <is>
+          <t>Analiza problemas del contexto profesional y social, a partir de información pertinente, para proponer soluciones fundamentadas, viables y contextualizadas.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -5745,21 +5634,19 @@
       <c r="I45" s="12" t="n">
         <v>81.90000000000001</v>
       </c>
-    </row>
+      <c r="J45" s="22" t="inlineStr">
+        <is>
+          <t>Gestiona su aprendizaje de manera autónoma para actualizar sus conocimientos y adaptar su desempeño a los cambios del entorno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="6" t="n"/>
-      <c r="G47" s="6" t="n"/>
-      <c r="H47" s="6" t="n"/>
-      <c r="I47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -5785,20 +5672,14 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
           <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
         </is>
       </c>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="6" t="n"/>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="6" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="6" t="n"/>
-      <c r="I52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -5843,12 +5724,6 @@
           <t>CE3 / CT1</t>
         </is>
       </c>
-      <c r="C55" s="16" t="n"/>
-      <c r="D55" s="16" t="n"/>
-      <c r="E55" s="16" t="n"/>
-      <c r="F55" s="16" t="n"/>
-      <c r="G55" s="16" t="n"/>
-      <c r="H55" s="16" t="n"/>
       <c r="I55" s="19" t="n">
         <v>98.2</v>
       </c>
@@ -5879,12 +5754,6 @@
           <t>CE3 / CT1</t>
         </is>
       </c>
-      <c r="C57" s="16" t="n"/>
-      <c r="D57" s="16" t="n"/>
-      <c r="E57" s="16" t="n"/>
-      <c r="F57" s="16" t="n"/>
-      <c r="G57" s="16" t="n"/>
-      <c r="H57" s="16" t="n"/>
       <c r="I57" s="19" t="n">
         <v>97.90000000000001</v>
       </c>
@@ -5915,12 +5784,6 @@
           <t>CE3 / CT1</t>
         </is>
       </c>
-      <c r="C59" s="16" t="n"/>
-      <c r="D59" s="16" t="n"/>
-      <c r="E59" s="16" t="n"/>
-      <c r="F59" s="16" t="n"/>
-      <c r="G59" s="16" t="n"/>
-      <c r="H59" s="16" t="n"/>
       <c r="I59" s="19" t="n">
         <v>97.3</v>
       </c>
@@ -5951,12 +5814,6 @@
           <t>CE3 / CT1</t>
         </is>
       </c>
-      <c r="C61" s="16" t="n"/>
-      <c r="D61" s="16" t="n"/>
-      <c r="E61" s="16" t="n"/>
-      <c r="F61" s="16" t="n"/>
-      <c r="G61" s="16" t="n"/>
-      <c r="H61" s="16" t="n"/>
       <c r="I61" s="19" t="n">
         <v>97</v>
       </c>
@@ -5987,12 +5844,6 @@
           <t>CE3 / CT1</t>
         </is>
       </c>
-      <c r="C63" s="16" t="n"/>
-      <c r="D63" s="16" t="n"/>
-      <c r="E63" s="16" t="n"/>
-      <c r="F63" s="16" t="n"/>
-      <c r="G63" s="16" t="n"/>
-      <c r="H63" s="16" t="n"/>
       <c r="I63" s="19" t="n">
         <v>96.09999999999999</v>
       </c>
@@ -6023,12 +5874,6 @@
           <t>CE4 / CT2</t>
         </is>
       </c>
-      <c r="C65" s="16" t="n"/>
-      <c r="D65" s="16" t="n"/>
-      <c r="E65" s="16" t="n"/>
-      <c r="F65" s="16" t="n"/>
-      <c r="G65" s="16" t="n"/>
-      <c r="H65" s="16" t="n"/>
       <c r="I65" s="19" t="n">
         <v>95.3</v>
       </c>
@@ -6059,12 +5904,6 @@
           <t>CE3 / CT1</t>
         </is>
       </c>
-      <c r="C67" s="16" t="n"/>
-      <c r="D67" s="16" t="n"/>
-      <c r="E67" s="16" t="n"/>
-      <c r="F67" s="16" t="n"/>
-      <c r="G67" s="16" t="n"/>
-      <c r="H67" s="16" t="n"/>
       <c r="I67" s="19" t="n">
         <v>93.8</v>
       </c>
@@ -6095,12 +5934,6 @@
           <t>CE4 / CT2</t>
         </is>
       </c>
-      <c r="C69" s="16" t="n"/>
-      <c r="D69" s="16" t="n"/>
-      <c r="E69" s="16" t="n"/>
-      <c r="F69" s="16" t="n"/>
-      <c r="G69" s="16" t="n"/>
-      <c r="H69" s="16" t="n"/>
       <c r="I69" s="19" t="n">
         <v>93.5</v>
       </c>
@@ -6123,8 +5956,8 @@
   </sheetData>
   <mergeCells count="43">
     <mergeCell ref="H38:I38"/>
+    <mergeCell ref="B68:H68"/>
     <mergeCell ref="B65:H65"/>
-    <mergeCell ref="B68:H68"/>
     <mergeCell ref="B55:H55"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="B30:H30"/>
@@ -6176,7 +6009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6185,6 +6018,7 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6201,20 +6035,13 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>══ TA1 — 60 estudiantes ══</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -6222,14 +6049,6 @@
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -6343,20 +6162,13 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -6404,6 +6216,11 @@
           <t>% Sobres.</t>
         </is>
       </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -6439,6 +6256,11 @@
       <c r="I12" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>Diseña productos, experiencias y servicios turísticos en contextos territoriales y organizacionales, garantizando innovación, sostenibilidad y estándares de calidad internacional.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -6474,6 +6296,11 @@
       <c r="I13" s="12" t="n">
         <v>100</v>
       </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>Formula estrategias de planificación y comercialización turística en destinos y organizaciones del sector, asegurando competitividad y posicionamiento en el mercado.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -6509,6 +6336,11 @@
       <c r="I14" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>Optimiza procesos de gestión y operación turística en empresas y emprendimientos del sector, garantizando eficiencia, rentabilidad y mejora continua.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -6544,6 +6376,11 @@
       <c r="I15" s="12" t="n">
         <v>100</v>
       </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>Evalúa proyectos y servicios turísticos en función del análisis de mercado y segmentación de la demanda, fundamentando decisiones estratégicas sostenibles.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -6579,6 +6416,11 @@
       <c r="I16" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>Utiliza tecnologías, datos y entornos digitales de manera crítica, segura y pertinente para gestionar información, interactuar responsablemente y generar soluciones de valor.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -6614,6 +6456,11 @@
       <c r="I17" s="12" t="n">
         <v>100</v>
       </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>Comunica ideas, argumentos y resultados de manera clara, estructurada y pertinente, para facilitar la comprensión, la colaboración y la toma de decisiones.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -6649,6 +6496,11 @@
       <c r="I18" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>Gestiona su aprendizaje de manera autónoma para actualizar sus conocimientos y adaptar su desempeño a los cambios del entorno.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -6684,21 +6536,19 @@
       <c r="I19" s="12" t="n">
         <v>100</v>
       </c>
-    </row>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>Analiza problemas del contexto profesional y social, a partir de información pertinente, para proponer soluciones fundamentadas, viables y contextualizadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -6724,20 +6574,14 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -6782,12 +6626,6 @@
           <t>CE1 / CT4</t>
         </is>
       </c>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
-      <c r="G29" s="16" t="n"/>
-      <c r="H29" s="16" t="n"/>
       <c r="I29" s="19" t="n">
         <v>100</v>
       </c>
@@ -6818,12 +6656,6 @@
           <t>CE1 / CT4</t>
         </is>
       </c>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
-      <c r="G31" s="16" t="n"/>
-      <c r="H31" s="16" t="n"/>
       <c r="I31" s="19" t="n">
         <v>100</v>
       </c>
@@ -6854,12 +6686,6 @@
           <t>CE1 / CT4</t>
         </is>
       </c>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
-      <c r="G33" s="16" t="n"/>
-      <c r="H33" s="16" t="n"/>
       <c r="I33" s="19" t="n">
         <v>100</v>
       </c>
@@ -6890,12 +6716,6 @@
           <t>CE2 / CT2</t>
         </is>
       </c>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
-      <c r="G35" s="16" t="n"/>
-      <c r="H35" s="16" t="n"/>
       <c r="I35" s="19" t="n">
         <v>100</v>
       </c>
@@ -6926,12 +6746,6 @@
           <t>CE2 / CT2</t>
         </is>
       </c>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
-      <c r="G37" s="16" t="n"/>
-      <c r="H37" s="16" t="n"/>
       <c r="I37" s="19" t="n">
         <v>100</v>
       </c>
@@ -6962,12 +6776,6 @@
           <t>CE2 / CT2</t>
         </is>
       </c>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
-      <c r="G39" s="16" t="n"/>
-      <c r="H39" s="16" t="n"/>
       <c r="I39" s="19" t="n">
         <v>100</v>
       </c>
@@ -6998,12 +6806,6 @@
           <t>CE3 / CT3</t>
         </is>
       </c>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
-      <c r="G41" s="16" t="n"/>
-      <c r="H41" s="16" t="n"/>
       <c r="I41" s="19" t="n">
         <v>100</v>
       </c>
@@ -7034,12 +6836,6 @@
           <t>CE3 / CT3</t>
         </is>
       </c>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
-      <c r="G43" s="16" t="n"/>
-      <c r="H43" s="16" t="n"/>
       <c r="I43" s="19" t="n">
         <v>100</v>
       </c>
@@ -7070,12 +6866,6 @@
           <t>CE3 / CT3</t>
         </is>
       </c>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
-      <c r="G45" s="16" t="n"/>
-      <c r="H45" s="16" t="n"/>
       <c r="I45" s="19" t="n">
         <v>100</v>
       </c>
@@ -7106,12 +6896,6 @@
           <t>CE4 / CT1</t>
         </is>
       </c>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
-      <c r="G47" s="16" t="n"/>
-      <c r="H47" s="16" t="n"/>
       <c r="I47" s="19" t="n">
         <v>100</v>
       </c>
@@ -7142,12 +6926,6 @@
           <t>CE4 / CT1</t>
         </is>
       </c>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
-      <c r="G49" s="16" t="n"/>
-      <c r="H49" s="16" t="n"/>
       <c r="I49" s="19" t="n">
         <v>100</v>
       </c>
@@ -7178,30 +6956,18 @@
           <t>CE4 / CT1</t>
         </is>
       </c>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
-      <c r="G51" s="16" t="n"/>
-      <c r="H51" s="16" t="n"/>
       <c r="I51" s="19" t="n">
         <v>100</v>
       </c>
     </row>
+    <row r="52"/>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
           <t>══ TA2 — 19 estudiantes ══</t>
         </is>
       </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="4" t="n"/>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -7209,14 +6975,6 @@
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B55" s="6" t="n"/>
-      <c r="C55" s="6" t="n"/>
-      <c r="D55" s="6" t="n"/>
-      <c r="E55" s="6" t="n"/>
-      <c r="F55" s="6" t="n"/>
-      <c r="G55" s="6" t="n"/>
-      <c r="H55" s="6" t="n"/>
-      <c r="I55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -7330,20 +7088,13 @@
         </is>
       </c>
     </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="6" t="n"/>
-      <c r="D60" s="6" t="n"/>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="6" t="n"/>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="6" t="n"/>
-      <c r="I60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
@@ -7391,6 +7142,11 @@
           <t>% Sobres.</t>
         </is>
       </c>
+      <c r="J61" s="21" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
@@ -7426,6 +7182,11 @@
       <c r="I62" s="8" t="n">
         <v>15.8</v>
       </c>
+      <c r="J62" s="22" t="inlineStr">
+        <is>
+          <t>Diseña productos, experiencias y servicios turísticos en contextos territoriales y organizacionales, garantizando innovación, sostenibilidad y estándares de calidad internacional.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
@@ -7461,6 +7222,11 @@
       <c r="I63" s="12" t="n">
         <v>47.4</v>
       </c>
+      <c r="J63" s="22" t="inlineStr">
+        <is>
+          <t>Formula estrategias de planificación y comercialización turística en destinos y organizaciones del sector, asegurando competitividad y posicionamiento en el mercado.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -7496,6 +7262,11 @@
       <c r="I64" s="8" t="n">
         <v>68.40000000000001</v>
       </c>
+      <c r="J64" s="22" t="inlineStr">
+        <is>
+          <t>Optimiza procesos de gestión y operación turística en empresas y emprendimientos del sector, garantizando eficiencia, rentabilidad y mejora continua.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
@@ -7531,6 +7302,11 @@
       <c r="I65" s="12" t="n">
         <v>31.6</v>
       </c>
+      <c r="J65" s="22" t="inlineStr">
+        <is>
+          <t>Evalúa proyectos y servicios turísticos en función del análisis de mercado y segmentación de la demanda, fundamentando decisiones estratégicas sostenibles.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
@@ -7566,6 +7342,11 @@
       <c r="I66" s="8" t="n">
         <v>31.6</v>
       </c>
+      <c r="J66" s="22" t="inlineStr">
+        <is>
+          <t>Utiliza tecnologías, datos y entornos digitales de manera crítica, segura y pertinente para gestionar información, interactuar responsablemente y generar soluciones de valor.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
@@ -7601,6 +7382,11 @@
       <c r="I67" s="12" t="n">
         <v>47.4</v>
       </c>
+      <c r="J67" s="22" t="inlineStr">
+        <is>
+          <t>Comunica ideas, argumentos y resultados de manera clara, estructurada y pertinente, para facilitar la comprensión, la colaboración y la toma de decisiones.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
@@ -7636,6 +7422,11 @@
       <c r="I68" s="8" t="n">
         <v>68.40000000000001</v>
       </c>
+      <c r="J68" s="22" t="inlineStr">
+        <is>
+          <t>Gestiona su aprendizaje de manera autónoma para actualizar sus conocimientos y adaptar su desempeño a los cambios del entorno.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
@@ -7671,21 +7462,19 @@
       <c r="I69" s="12" t="n">
         <v>15.8</v>
       </c>
-    </row>
+      <c r="J69" s="22" t="inlineStr">
+        <is>
+          <t>Analiza problemas del contexto profesional y social, a partir de información pertinente, para proponer soluciones fundamentadas, viables y contextualizadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70"/>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B71" s="6" t="n"/>
-      <c r="C71" s="6" t="n"/>
-      <c r="D71" s="6" t="n"/>
-      <c r="E71" s="6" t="n"/>
-      <c r="F71" s="6" t="n"/>
-      <c r="G71" s="6" t="n"/>
-      <c r="H71" s="6" t="n"/>
-      <c r="I71" s="6" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
@@ -7711,20 +7500,14 @@
         </is>
       </c>
     </row>
+    <row r="74"/>
+    <row r="75"/>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
           <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
         </is>
       </c>
-      <c r="B76" s="6" t="n"/>
-      <c r="C76" s="6" t="n"/>
-      <c r="D76" s="6" t="n"/>
-      <c r="E76" s="6" t="n"/>
-      <c r="F76" s="6" t="n"/>
-      <c r="G76" s="6" t="n"/>
-      <c r="H76" s="6" t="n"/>
-      <c r="I76" s="6" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -7769,12 +7552,6 @@
           <t>CE3 / CT3</t>
         </is>
       </c>
-      <c r="C79" s="16" t="n"/>
-      <c r="D79" s="16" t="n"/>
-      <c r="E79" s="16" t="n"/>
-      <c r="F79" s="16" t="n"/>
-      <c r="G79" s="16" t="n"/>
-      <c r="H79" s="16" t="n"/>
       <c r="I79" s="19" t="n">
         <v>100</v>
       </c>
@@ -7805,12 +7582,6 @@
           <t>CE2 / CT2</t>
         </is>
       </c>
-      <c r="C81" s="16" t="n"/>
-      <c r="D81" s="16" t="n"/>
-      <c r="E81" s="16" t="n"/>
-      <c r="F81" s="16" t="n"/>
-      <c r="G81" s="16" t="n"/>
-      <c r="H81" s="16" t="n"/>
       <c r="I81" s="19" t="n">
         <v>100</v>
       </c>
@@ -7841,12 +7612,6 @@
           <t>CE3 / CT3</t>
         </is>
       </c>
-      <c r="C83" s="16" t="n"/>
-      <c r="D83" s="16" t="n"/>
-      <c r="E83" s="16" t="n"/>
-      <c r="F83" s="16" t="n"/>
-      <c r="G83" s="16" t="n"/>
-      <c r="H83" s="16" t="n"/>
       <c r="I83" s="19" t="n">
         <v>94.7</v>
       </c>
@@ -7877,12 +7642,6 @@
           <t>CE1 / CT4</t>
         </is>
       </c>
-      <c r="C85" s="16" t="n"/>
-      <c r="D85" s="16" t="n"/>
-      <c r="E85" s="16" t="n"/>
-      <c r="F85" s="16" t="n"/>
-      <c r="G85" s="16" t="n"/>
-      <c r="H85" s="16" t="n"/>
       <c r="I85" s="19" t="n">
         <v>94.7</v>
       </c>
@@ -7950,7 +7709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7959,6 +7718,7 @@
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7975,20 +7735,13 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>══ TA1 — 42 estudiantes ══</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -7996,14 +7749,6 @@
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -8117,20 +7862,13 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -8178,6 +7916,11 @@
           <t>% Sobres.</t>
         </is>
       </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -8213,6 +7956,11 @@
       <c r="I12" s="8" t="n">
         <v>92.90000000000001</v>
       </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>Diseña productos turísticos incorporando TIC's, saberes ancestrales, interculturalidad y equidad de género, para generar valor social, económico y cultural.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -8248,6 +7996,11 @@
       <c r="I13" s="12" t="n">
         <v>71.40000000000001</v>
       </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>Interpreta áreas naturales y patrimoniales mediante principios de educación ambiental y sostenibilidad para promover una participación turística responsable y bio-consciente.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -8283,6 +8036,11 @@
       <c r="I14" s="8" t="n">
         <v>88.09999999999999</v>
       </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>Aplica herramientas tecnológicas y trabajo multidisciplinario para mejorar la gestión y operación turística sostenible.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -8318,6 +8076,11 @@
       <c r="I15" s="12" t="n">
         <v>92.90000000000001</v>
       </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>Analiza problemas del contexto profesional y social, a partir de información pertinente, para proponer soluciones fundamentadas, viables y contextualizadas.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -8353,6 +8116,11 @@
       <c r="I16" s="8" t="n">
         <v>81</v>
       </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>Gestiona su aprendizaje de manera autónoma para actualizar sus conocimientos y adaptar su desempeño a los cambios del entorno.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -8388,6 +8156,11 @@
       <c r="I17" s="12" t="n">
         <v>85.7</v>
       </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>Comunica ideas, argumentos y resultados de manera clara, estructurada y pertinente, para facilitar la comprensión, la colaboración y la toma de decisiones.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -8423,21 +8196,19 @@
       <c r="I18" s="8" t="n">
         <v>88.09999999999999</v>
       </c>
-    </row>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>Utiliza tecnologías, datos y entornos digitales de manera crítica, segura y pertinente para gestionar información, interactuar responsablemente y generar soluciones de valor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -8463,20 +8234,14 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -8521,12 +8286,6 @@
           <t>CT3</t>
         </is>
       </c>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
-      <c r="G28" s="16" t="n"/>
-      <c r="H28" s="16" t="n"/>
       <c r="I28" s="19" t="n">
         <v>100</v>
       </c>
@@ -8557,12 +8316,6 @@
           <t>CE1 / CT1</t>
         </is>
       </c>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
-      <c r="G30" s="16" t="n"/>
-      <c r="H30" s="16" t="n"/>
       <c r="I30" s="19" t="n">
         <v>100</v>
       </c>
@@ -8593,12 +8346,6 @@
           <t>CE2 / CT3</t>
         </is>
       </c>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
-      <c r="G32" s="16" t="n"/>
-      <c r="H32" s="16" t="n"/>
       <c r="I32" s="19" t="n">
         <v>100</v>
       </c>
@@ -8629,12 +8376,6 @@
           <t>CE3 / CT4</t>
         </is>
       </c>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
-      <c r="G34" s="16" t="n"/>
-      <c r="H34" s="16" t="n"/>
       <c r="I34" s="19" t="n">
         <v>100</v>
       </c>
@@ -8665,12 +8406,6 @@
           <t>CE1 / CT1</t>
         </is>
       </c>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-      <c r="G36" s="16" t="n"/>
-      <c r="H36" s="16" t="n"/>
       <c r="I36" s="19" t="n">
         <v>100</v>
       </c>
@@ -8701,12 +8436,6 @@
           <t>CE3 / CT4</t>
         </is>
       </c>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
-      <c r="G38" s="16" t="n"/>
-      <c r="H38" s="16" t="n"/>
       <c r="I38" s="19" t="n">
         <v>97.59999999999999</v>
       </c>
@@ -8737,12 +8466,6 @@
           <t>CE2 / CT3</t>
         </is>
       </c>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
-      <c r="G40" s="16" t="n"/>
-      <c r="H40" s="16" t="n"/>
       <c r="I40" s="19" t="n">
         <v>97.59999999999999</v>
       </c>
@@ -8773,12 +8496,6 @@
           <t>CT2</t>
         </is>
       </c>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
-      <c r="G42" s="16" t="n"/>
-      <c r="H42" s="16" t="n"/>
       <c r="I42" s="19" t="n">
         <v>97.59999999999999</v>
       </c>
@@ -8809,12 +8526,6 @@
           <t>CT3</t>
         </is>
       </c>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
-      <c r="G44" s="16" t="n"/>
-      <c r="H44" s="16" t="n"/>
       <c r="I44" s="19" t="n">
         <v>95.2</v>
       </c>
@@ -8845,12 +8556,6 @@
           <t>CT2</t>
         </is>
       </c>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
-      <c r="G46" s="16" t="n"/>
-      <c r="H46" s="16" t="n"/>
       <c r="I46" s="19" t="n">
         <v>95.2</v>
       </c>
@@ -8881,12 +8586,6 @@
           <t>CT3</t>
         </is>
       </c>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
-      <c r="G48" s="16" t="n"/>
-      <c r="H48" s="16" t="n"/>
       <c r="I48" s="19" t="n">
         <v>95.2</v>
       </c>
@@ -8917,12 +8616,6 @@
           <t>CT3</t>
         </is>
       </c>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="16" t="n"/>
-      <c r="E50" s="16" t="n"/>
-      <c r="F50" s="16" t="n"/>
-      <c r="G50" s="16" t="n"/>
-      <c r="H50" s="16" t="n"/>
       <c r="I50" s="19" t="n">
         <v>92.90000000000001</v>
       </c>
@@ -8953,12 +8646,6 @@
           <t>CE2 / CT3</t>
         </is>
       </c>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="n"/>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
-      <c r="G52" s="16" t="n"/>
-      <c r="H52" s="16" t="n"/>
       <c r="I52" s="19" t="n">
         <v>90.5</v>
       </c>
@@ -8978,20 +8665,14 @@
         <v>90.5</v>
       </c>
     </row>
+    <row r="54"/>
+    <row r="55"/>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
           <t>══ TA2 — 95 estudiantes ══</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -8999,14 +8680,6 @@
           <t>Resultado global de cohorte</t>
         </is>
       </c>
-      <c r="B57" s="6" t="n"/>
-      <c r="C57" s="6" t="n"/>
-      <c r="D57" s="6" t="n"/>
-      <c r="E57" s="6" t="n"/>
-      <c r="F57" s="6" t="n"/>
-      <c r="G57" s="6" t="n"/>
-      <c r="H57" s="6" t="n"/>
-      <c r="I57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -9120,20 +8793,13 @@
         </is>
       </c>
     </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
           <t>Logro y distribución por competencia</t>
         </is>
       </c>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="6" t="n"/>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="6" t="n"/>
-      <c r="F62" s="6" t="n"/>
-      <c r="G62" s="6" t="n"/>
-      <c r="H62" s="6" t="n"/>
-      <c r="I62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -9181,6 +8847,11 @@
           <t>% Sobres.</t>
         </is>
       </c>
+      <c r="J63" s="21" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -9216,6 +8887,11 @@
       <c r="I64" s="8" t="n">
         <v>86.3</v>
       </c>
+      <c r="J64" s="22" t="inlineStr">
+        <is>
+          <t>Diseña productos turísticos incorporando TIC's, saberes ancestrales, interculturalidad y equidad de género, para generar valor social, económico y cultural.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
@@ -9251,6 +8927,11 @@
       <c r="I65" s="12" t="n">
         <v>92.59999999999999</v>
       </c>
+      <c r="J65" s="22" t="inlineStr">
+        <is>
+          <t>Interpreta áreas naturales y patrimoniales mediante principios de educación ambiental y sostenibilidad para promover una participación turística responsable y bio-consciente.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
@@ -9286,6 +8967,11 @@
       <c r="I66" s="8" t="n">
         <v>90.5</v>
       </c>
+      <c r="J66" s="22" t="inlineStr">
+        <is>
+          <t>Aplica herramientas tecnológicas y trabajo multidisciplinario para mejorar la gestión y operación turística sostenible.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
@@ -9321,6 +9007,11 @@
       <c r="I67" s="12" t="n">
         <v>91.59999999999999</v>
       </c>
+      <c r="J67" s="22" t="inlineStr">
+        <is>
+          <t>Formula proyectos turísticos innovadores para implementar iniciativas alineadas a políticas públicas y tendencias globales.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
@@ -9356,6 +9047,11 @@
       <c r="I68" s="8" t="n">
         <v>90.5</v>
       </c>
+      <c r="J68" s="22" t="inlineStr">
+        <is>
+          <t>Analiza problemas del contexto profesional y social, a partir de información pertinente, para proponer soluciones fundamentadas, viables y contextualizadas.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
@@ -9391,6 +9087,11 @@
       <c r="I69" s="12" t="n">
         <v>74.7</v>
       </c>
+      <c r="J69" s="22" t="inlineStr">
+        <is>
+          <t>Gestiona su aprendizaje de manera autónoma para actualizar sus conocimientos y adaptar su desempeño a los cambios del entorno.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
@@ -9426,6 +9127,11 @@
       <c r="I70" s="8" t="n">
         <v>92.59999999999999</v>
       </c>
+      <c r="J70" s="22" t="inlineStr">
+        <is>
+          <t>Comunica ideas, argumentos y resultados de manera clara, estructurada y pertinente, para facilitar la comprensión, la colaboración y la toma de decisiones.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
@@ -9461,21 +9167,19 @@
       <c r="I71" s="12" t="n">
         <v>90.5</v>
       </c>
-    </row>
+      <c r="J71" s="22" t="inlineStr">
+        <is>
+          <t>Utiliza tecnologías, datos y entornos digitales de manera crítica, segura y pertinente para gestionar información, interactuar responsablemente y generar soluciones de valor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72"/>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Ítems críticos (&lt;50% de aciertos, nivel Insuficiente)</t>
         </is>
       </c>
-      <c r="B73" s="6" t="n"/>
-      <c r="C73" s="6" t="n"/>
-      <c r="D73" s="6" t="n"/>
-      <c r="E73" s="6" t="n"/>
-      <c r="F73" s="6" t="n"/>
-      <c r="G73" s="6" t="n"/>
-      <c r="H73" s="6" t="n"/>
-      <c r="I73" s="6" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -9501,20 +9205,14 @@
         </is>
       </c>
     </row>
+    <row r="76"/>
+    <row r="77"/>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
           <t>Ítems sobresalientes (≥90% de aciertos, nivel Sobresaliente)</t>
         </is>
       </c>
-      <c r="B78" s="6" t="n"/>
-      <c r="C78" s="6" t="n"/>
-      <c r="D78" s="6" t="n"/>
-      <c r="E78" s="6" t="n"/>
-      <c r="F78" s="6" t="n"/>
-      <c r="G78" s="6" t="n"/>
-      <c r="H78" s="6" t="n"/>
-      <c r="I78" s="6" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -9559,12 +9257,6 @@
           <t>CT3</t>
         </is>
       </c>
-      <c r="C81" s="16" t="n"/>
-      <c r="D81" s="16" t="n"/>
-      <c r="E81" s="16" t="n"/>
-      <c r="F81" s="16" t="n"/>
-      <c r="G81" s="16" t="n"/>
-      <c r="H81" s="16" t="n"/>
       <c r="I81" s="19" t="n">
         <v>100</v>
       </c>
@@ -9595,12 +9287,6 @@
           <t>CT3</t>
         </is>
       </c>
-      <c r="C83" s="16" t="n"/>
-      <c r="D83" s="16" t="n"/>
-      <c r="E83" s="16" t="n"/>
-      <c r="F83" s="16" t="n"/>
-      <c r="G83" s="16" t="n"/>
-      <c r="H83" s="16" t="n"/>
       <c r="I83" s="19" t="n">
         <v>98.90000000000001</v>
       </c>
@@ -9631,12 +9317,6 @@
           <t>CE3 / CT4</t>
         </is>
       </c>
-      <c r="C85" s="16" t="n"/>
-      <c r="D85" s="16" t="n"/>
-      <c r="E85" s="16" t="n"/>
-      <c r="F85" s="16" t="n"/>
-      <c r="G85" s="16" t="n"/>
-      <c r="H85" s="16" t="n"/>
       <c r="I85" s="19" t="n">
         <v>98.90000000000001</v>
       </c>
@@ -9667,12 +9347,6 @@
           <t>CT3</t>
         </is>
       </c>
-      <c r="C87" s="16" t="n"/>
-      <c r="D87" s="16" t="n"/>
-      <c r="E87" s="16" t="n"/>
-      <c r="F87" s="16" t="n"/>
-      <c r="G87" s="16" t="n"/>
-      <c r="H87" s="16" t="n"/>
       <c r="I87" s="19" t="n">
         <v>98.90000000000001</v>
       </c>
@@ -9703,12 +9377,6 @@
           <t>CE1 / CE4</t>
         </is>
       </c>
-      <c r="C89" s="16" t="n"/>
-      <c r="D89" s="16" t="n"/>
-      <c r="E89" s="16" t="n"/>
-      <c r="F89" s="16" t="n"/>
-      <c r="G89" s="16" t="n"/>
-      <c r="H89" s="16" t="n"/>
       <c r="I89" s="19" t="n">
         <v>98.90000000000001</v>
       </c>
@@ -9739,12 +9407,6 @@
           <t>CE1 / CE4</t>
         </is>
       </c>
-      <c r="C91" s="16" t="n"/>
-      <c r="D91" s="16" t="n"/>
-      <c r="E91" s="16" t="n"/>
-      <c r="F91" s="16" t="n"/>
-      <c r="G91" s="16" t="n"/>
-      <c r="H91" s="16" t="n"/>
       <c r="I91" s="19" t="n">
         <v>97.90000000000001</v>
       </c>
@@ -9775,12 +9437,6 @@
           <t>CE2 / CT3</t>
         </is>
       </c>
-      <c r="C93" s="16" t="n"/>
-      <c r="D93" s="16" t="n"/>
-      <c r="E93" s="16" t="n"/>
-      <c r="F93" s="16" t="n"/>
-      <c r="G93" s="16" t="n"/>
-      <c r="H93" s="16" t="n"/>
       <c r="I93" s="19" t="n">
         <v>97.90000000000001</v>
       </c>
@@ -9811,12 +9467,6 @@
           <t>CE4 / CT2</t>
         </is>
       </c>
-      <c r="C95" s="16" t="n"/>
-      <c r="D95" s="16" t="n"/>
-      <c r="E95" s="16" t="n"/>
-      <c r="F95" s="16" t="n"/>
-      <c r="G95" s="16" t="n"/>
-      <c r="H95" s="16" t="n"/>
       <c r="I95" s="19" t="n">
         <v>97.90000000000001</v>
       </c>
@@ -9847,12 +9497,6 @@
           <t>CE1 / CT1</t>
         </is>
       </c>
-      <c r="C97" s="16" t="n"/>
-      <c r="D97" s="16" t="n"/>
-      <c r="E97" s="16" t="n"/>
-      <c r="F97" s="16" t="n"/>
-      <c r="G97" s="16" t="n"/>
-      <c r="H97" s="16" t="n"/>
       <c r="I97" s="19" t="n">
         <v>96.8</v>
       </c>
@@ -9883,12 +9527,6 @@
           <t>CE1 / CT1</t>
         </is>
       </c>
-      <c r="C99" s="16" t="n"/>
-      <c r="D99" s="16" t="n"/>
-      <c r="E99" s="16" t="n"/>
-      <c r="F99" s="16" t="n"/>
-      <c r="G99" s="16" t="n"/>
-      <c r="H99" s="16" t="n"/>
       <c r="I99" s="19" t="n">
         <v>96.8</v>
       </c>
@@ -9919,12 +9557,6 @@
           <t>CE3 / CT4</t>
         </is>
       </c>
-      <c r="C101" s="16" t="n"/>
-      <c r="D101" s="16" t="n"/>
-      <c r="E101" s="16" t="n"/>
-      <c r="F101" s="16" t="n"/>
-      <c r="G101" s="16" t="n"/>
-      <c r="H101" s="16" t="n"/>
       <c r="I101" s="19" t="n">
         <v>96.8</v>
       </c>
@@ -9955,12 +9587,6 @@
           <t>CE3 / CT4</t>
         </is>
       </c>
-      <c r="C103" s="16" t="n"/>
-      <c r="D103" s="16" t="n"/>
-      <c r="E103" s="16" t="n"/>
-      <c r="F103" s="16" t="n"/>
-      <c r="G103" s="16" t="n"/>
-      <c r="H103" s="16" t="n"/>
       <c r="I103" s="19" t="n">
         <v>96.8</v>
       </c>
@@ -9991,12 +9617,6 @@
           <t>CE4 / CT2</t>
         </is>
       </c>
-      <c r="C105" s="16" t="n"/>
-      <c r="D105" s="16" t="n"/>
-      <c r="E105" s="16" t="n"/>
-      <c r="F105" s="16" t="n"/>
-      <c r="G105" s="16" t="n"/>
-      <c r="H105" s="16" t="n"/>
       <c r="I105" s="19" t="n">
         <v>96.8</v>
       </c>
@@ -10027,12 +9647,6 @@
           <t>CE4 / CT2</t>
         </is>
       </c>
-      <c r="C107" s="16" t="n"/>
-      <c r="D107" s="16" t="n"/>
-      <c r="E107" s="16" t="n"/>
-      <c r="F107" s="16" t="n"/>
-      <c r="G107" s="16" t="n"/>
-      <c r="H107" s="16" t="n"/>
       <c r="I107" s="19" t="n">
         <v>95.8</v>
       </c>

--- a/data/Cuadros_oficiales_por_carrera.xlsx
+++ b/data/Cuadros_oficiales_por_carrera.xlsx
@@ -549,7 +549,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -676,7 +675,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -1056,7 +1054,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
@@ -1141,8 +1138,6 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
@@ -1212,8 +1207,6 @@
         <v>91.2</v>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
@@ -1340,7 +1333,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
@@ -1720,7 +1712,6 @@
         </is>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
@@ -1775,8 +1766,6 @@
         <v>31.7</v>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58"/>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
@@ -2386,7 +2375,7 @@
       </c>
       <c r="J15" s="22" t="inlineStr">
         <is>
-          <t>Analiza situaciones profesionales y toma decisiones fundamentadas considerando impactos sociales, ambientales, económicos y tecnológicos, actuando con responsabilidad, integridad y compromiso con el desarrollo sostenible en contextos locales y globales.</t>
+          <t>Analiza problemas del contexto profesional y social, a partir de información pertinente, para proponer soluciones fundamentadas, viables y contextualizadas.</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2415,7 @@
       </c>
       <c r="J16" s="22" t="inlineStr">
         <is>
-          <t>Comunica ideas con claridad y sustento técnico, y colabora eficazmente en equipos diversos e interdisciplinarios, contribuyendo activamente a la construcción de soluciones en entornos profesionales, multiculturales y digitales.</t>
+          <t>Comunica ideas, argumentos y resultados de manera clara, estructurada y pertinente, para facilitar la comprensión, la colaboración y la toma de decisiones.</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2455,7 @@
       </c>
       <c r="J17" s="22" t="inlineStr">
         <is>
-          <t>Gestiona información y conocimiento con rigor metodológico, actualizándose de manera autónoma y aplicando nuevos saberes para resolver problemas complejos en contextos dinámicos y cambiantes.</t>
+          <t>Gestiona su aprendizaje de manera autónoma para actualizar sus conocimientos y adaptar su desempeño a los cambios del entorno.</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2495,7 @@
       </c>
       <c r="J18" s="22" t="inlineStr">
         <is>
-          <t>Integra tecnologías digitales, análisis de datos y herramientas emergentes de manera crítica, ética y estratégica para generar soluciones pertinentes y sostenibles en contextos profesionales y sociales.</t>
+          <t>Utiliza tecnologías, datos y entornos digitales de manera crítica, segura y pertinente para gestionar información, interactuar responsablemente y generar soluciones de valor.</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3009,7 @@
       </c>
       <c r="J45" s="22" t="inlineStr">
         <is>
-          <t>Analiza situaciones profesionales y toma decisiones fundamentadas considerando impactos sociales, ambientales, económicos y tecnológicos, actuando con responsabilidad, integridad y compromiso con el desarrollo sostenible en contextos locales y globales.</t>
+          <t>Analiza problemas del contexto profesional y social, a partir de información pertinente, para proponer soluciones fundamentadas, viables y contextualizadas.</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3049,7 @@
       </c>
       <c r="J46" s="22" t="inlineStr">
         <is>
-          <t>Comunica ideas con claridad y sustento técnico, y colabora eficazmente en equipos diversos e interdisciplinarios, contribuyendo activamente a la construcción de soluciones en entornos profesionales, multiculturales y digitales.</t>
+          <t>Comunica ideas, argumentos y resultados de manera clara, estructurada y pertinente, para facilitar la comprensión, la colaboración y la toma de decisiones.</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3089,7 @@
       </c>
       <c r="J47" s="22" t="inlineStr">
         <is>
-          <t>Gestiona información y conocimiento con rigor metodológico, actualizándose de manera autónoma y aplicando nuevos saberes para resolver problemas complejos en contextos dinámicos y cambiantes.</t>
+          <t>Gestiona su aprendizaje de manera autónoma para actualizar sus conocimientos y adaptar su desempeño a los cambios del entorno.</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3129,7 @@
       </c>
       <c r="J48" s="22" t="inlineStr">
         <is>
-          <t>Integra tecnologías digitales, análisis de datos y herramientas emergentes de manera crítica, ética y estratégica para generar soluciones pertinentes y sostenibles en contextos profesionales y sociales.</t>
+          <t>Utiliza tecnologías, datos y entornos digitales de manera crítica, segura y pertinente para gestionar información, interactuar responsablemente y generar soluciones de valor.</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3422,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3560,7 +3548,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -3900,7 +3887,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
@@ -4045,8 +4031,6 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
@@ -4116,8 +4100,6 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
@@ -4244,7 +4226,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
@@ -4584,7 +4565,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
@@ -4654,8 +4634,6 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
@@ -4767,7 +4745,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4894,7 +4871,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -5114,7 +5090,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
@@ -5146,8 +5121,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
@@ -5292,8 +5265,6 @@
         <v>90.3</v>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
@@ -5420,7 +5391,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
@@ -5640,7 +5610,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
@@ -5672,8 +5641,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
@@ -6035,7 +6002,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -6162,7 +6128,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -6542,7 +6507,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
@@ -6574,8 +6538,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
@@ -6960,8 +6922,6 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
@@ -7088,7 +7048,6 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
@@ -7468,7 +7427,6 @@
         </is>
       </c>
     </row>
-    <row r="70"/>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
@@ -7500,8 +7458,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75"/>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
@@ -7735,7 +7691,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -7862,7 +7817,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -8202,7 +8156,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
@@ -8234,8 +8187,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
@@ -8665,8 +8616,6 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="54"/>
-    <row r="55"/>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
@@ -8793,7 +8742,6 @@
         </is>
       </c>
     </row>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
@@ -9173,7 +9121,6 @@
         </is>
       </c>
     </row>
-    <row r="72"/>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
@@ -9205,8 +9152,6 @@
         </is>
       </c>
     </row>
-    <row r="76"/>
-    <row r="77"/>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
